--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135312324</v>
+        <v>135357241</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granliden, Granliden, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657559</v>
+        <v>658183</v>
       </c>
       <c r="R2" t="n">
-        <v>7328362</v>
+        <v>7328256</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,15 +770,2363 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135357246</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80489</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658109</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7328220</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Massor på gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135357242</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>658183</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7328256</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135357243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>658141</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7328242</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135357245</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>658102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7328232</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135357244</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658102</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7328232</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135357249</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>658109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7328220</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135357247</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>658109</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7328220</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135357256</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97435</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>658015</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7328371</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135357254</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7328373</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135357258</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>657969</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7328406</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135357261</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>657939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7328422</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135312324</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granliden, Granliden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>657559</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7328362</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135357255</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7328373</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135357252</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>658041</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135357250</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>658064</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7328265</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135357251</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>658041</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135357253</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>657993</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7328350</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135357259</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>657958</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7328432</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135357262</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>657758</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7328354</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135357260</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>657949</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7328433</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135357257</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>657988</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7328384</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135357242</v>
+        <v>135356932</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658183</v>
+        <v>658170</v>
       </c>
       <c r="R4" t="n">
-        <v>7328256</v>
+        <v>7328245</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,12 +1001,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135357243</v>
+        <v>135356933</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658141</v>
+        <v>658134</v>
       </c>
       <c r="R5" t="n">
-        <v>7328242</v>
+        <v>7328255</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135357245</v>
+        <v>135357242</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658102</v>
+        <v>658183</v>
       </c>
       <c r="R6" t="n">
-        <v>7328232</v>
+        <v>7328256</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,32 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135357244</v>
+        <v>135357243</v>
       </c>
       <c r="B7" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658102</v>
+        <v>658141</v>
       </c>
       <c r="R7" t="n">
-        <v>7328232</v>
+        <v>7328242</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,27 +1350,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135357249</v>
+        <v>135357245</v>
       </c>
       <c r="B8" t="n">
-        <v>80499</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658109</v>
+        <v>658102</v>
       </c>
       <c r="R8" t="n">
-        <v>7328220</v>
+        <v>7328232</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135357247</v>
+        <v>135358232</v>
       </c>
       <c r="B9" t="n">
-        <v>80500</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>658109</v>
+        <v>658139</v>
       </c>
       <c r="R9" t="n">
-        <v>7328220</v>
+        <v>7328222</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,19 +1529,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,12 +1546,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1572,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135357256</v>
+        <v>135358233</v>
       </c>
       <c r="B10" t="n">
-        <v>97435</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,13 +1597,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658015</v>
+        <v>658108</v>
       </c>
       <c r="R10" t="n">
-        <v>7328371</v>
+        <v>7328200</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,19 +1630,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,12 +1647,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1683,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135357254</v>
+        <v>135358234</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,13 +1698,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658009</v>
+        <v>658060</v>
       </c>
       <c r="R11" t="n">
-        <v>7328373</v>
+        <v>7328226</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,19 +1731,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,12 +1748,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1794,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135357258</v>
+        <v>135356934</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>83358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657969</v>
+        <v>658125</v>
       </c>
       <c r="R12" t="n">
-        <v>7328406</v>
+        <v>7328199</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,12 +1859,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1905,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135357261</v>
+        <v>135357244</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>83358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657939</v>
+        <v>658102</v>
       </c>
       <c r="R13" t="n">
-        <v>7328422</v>
+        <v>7328232</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,48 +1986,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135312324</v>
+        <v>135357249</v>
       </c>
       <c r="B14" t="n">
-        <v>91970</v>
+        <v>80499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granliden, Granliden, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657559</v>
+        <v>658109</v>
       </c>
       <c r="R14" t="n">
-        <v>7328362</v>
+        <v>7328220</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,12 +2051,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,44 +2081,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135357255</v>
+        <v>135357247</v>
       </c>
       <c r="B15" t="n">
-        <v>91974</v>
+        <v>80500</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2148,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>658009</v>
+        <v>658109</v>
       </c>
       <c r="R15" t="n">
-        <v>7328373</v>
+        <v>7328220</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2167,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2177,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135357252</v>
+        <v>135357256</v>
       </c>
       <c r="B16" t="n">
-        <v>83222</v>
+        <v>97435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658041</v>
+        <v>658015</v>
       </c>
       <c r="R16" t="n">
-        <v>7328283</v>
+        <v>7328371</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2294,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2304,7 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,32 +2319,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135357250</v>
+        <v>135356943</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>89354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,13 +2354,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658064</v>
+        <v>658013</v>
       </c>
       <c r="R17" t="n">
-        <v>7328265</v>
+        <v>7328309</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,12 +2414,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2446,32 +2430,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135357251</v>
+        <v>135356953</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658041</v>
+        <v>658084</v>
       </c>
       <c r="R18" t="n">
-        <v>7328283</v>
+        <v>7328414</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,7 +2500,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2510,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,12 +2525,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2557,32 +2541,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135357253</v>
+        <v>135357254</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657993</v>
+        <v>658009</v>
       </c>
       <c r="R19" t="n">
-        <v>7328350</v>
+        <v>7328373</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2611,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2621,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,32 +2652,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135357259</v>
+        <v>135357258</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2703,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657958</v>
+        <v>657969</v>
       </c>
       <c r="R20" t="n">
-        <v>7328432</v>
+        <v>7328406</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,7 +2722,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2748,7 +2732,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,32 +2763,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135357262</v>
+        <v>135357261</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2814,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>657758</v>
+        <v>657939</v>
       </c>
       <c r="R21" t="n">
-        <v>7328354</v>
+        <v>7328422</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,7 +2833,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2843,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,60 +2874,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135357260</v>
+        <v>135356944</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>79452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>657949</v>
+        <v>658000</v>
       </c>
       <c r="R22" t="n">
-        <v>7328433</v>
+        <v>7328356</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,7 +2944,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,12 +2954,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,19 +2963,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3019,48 +2985,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135357257</v>
+        <v>135312324</v>
       </c>
       <c r="B23" t="n">
-        <v>99217</v>
+        <v>91970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Granliden, Granliden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>657988</v>
+        <v>657559</v>
       </c>
       <c r="R23" t="n">
-        <v>7328384</v>
+        <v>7328362</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3084,22 +3050,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,15 +3070,2784 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135357255</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7328373</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135356949</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>658015</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7328401</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135357252</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>658041</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135356945</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>657999</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7328359</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135356947</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>657973</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7328369</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135356936</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>658123</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7328269</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135356938</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>658123</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7328290</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135356939</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>658104</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7328291</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135356940</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>658075</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7328297</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135356941</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>658052</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7328288</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135356946</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>657993</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7328349</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135356948</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>658007</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7328388</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135356951</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>658045</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7328393</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135356952</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>658067</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7328396</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135357250</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>658064</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7328265</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135357251</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>658041</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135357253</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>657993</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7328350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135357259</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>657958</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7328432</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135357262</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>657758</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7328354</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135356935</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>658122</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7328267</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135356950</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>658045</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7328393</v>
+      </c>
+      <c r="S44" t="n">
+        <v>9</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135357260</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>657949</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7328433</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135357257</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>657988</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7328384</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135358229</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>658194</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7328255</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135358230</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>658217</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7328285</v>
+      </c>
+      <c r="S48" t="n">
+        <v>14</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135357241</v>
+        <v>135358883</v>
       </c>
       <c r="B2" t="n">
-        <v>83222</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658183</v>
+        <v>658064</v>
       </c>
       <c r="R2" t="n">
-        <v>7328256</v>
+        <v>7328238</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135357246</v>
+        <v>135358885</v>
       </c>
       <c r="B3" t="n">
-        <v>80489</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658109</v>
+        <v>658061</v>
       </c>
       <c r="R3" t="n">
-        <v>7328220</v>
+        <v>7328238</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,12 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Massor på gammal sälg.</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,19 +875,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -906,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135356932</v>
+        <v>135358874</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658170</v>
+        <v>658085</v>
       </c>
       <c r="R4" t="n">
-        <v>7328245</v>
+        <v>7328254</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,12 +992,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1017,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135356933</v>
+        <v>135358881</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658134</v>
+        <v>658070</v>
       </c>
       <c r="R5" t="n">
-        <v>7328255</v>
+        <v>7328235</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1128,32 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135357242</v>
+        <v>135357241</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135357243</v>
+        <v>135358900</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658141</v>
+        <v>658004</v>
       </c>
       <c r="R7" t="n">
-        <v>7328242</v>
+        <v>7328256</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1350,45 +1341,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135357245</v>
+        <v>135357246</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>80489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658102</v>
+        <v>658109</v>
       </c>
       <c r="R8" t="n">
-        <v>7328232</v>
+        <v>7328220</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1424,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Massor på gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,6 +1438,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135358232</v>
+        <v>135356932</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>658139</v>
+        <v>658170</v>
       </c>
       <c r="R9" t="n">
-        <v>7328222</v>
+        <v>7328245</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,9 +1529,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,12 +1556,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1562,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135358233</v>
+        <v>135356933</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1597,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658108</v>
+        <v>658134</v>
       </c>
       <c r="R10" t="n">
-        <v>7328200</v>
+        <v>7328255</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,9 +1640,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,12 +1667,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1663,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135358234</v>
+        <v>135357242</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1698,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658060</v>
+        <v>658183</v>
       </c>
       <c r="R11" t="n">
-        <v>7328226</v>
+        <v>7328256</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,9 +1751,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,12 +1778,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1764,32 +1794,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135356934</v>
+        <v>135357243</v>
       </c>
       <c r="B12" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658125</v>
+        <v>658141</v>
       </c>
       <c r="R12" t="n">
-        <v>7328199</v>
+        <v>7328242</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1834,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,12 +1889,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1875,32 +1905,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135357244</v>
+        <v>135357245</v>
       </c>
       <c r="B13" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,27 +2016,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135357249</v>
+        <v>135358232</v>
       </c>
       <c r="B14" t="n">
-        <v>80499</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2021,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658109</v>
+        <v>658139</v>
       </c>
       <c r="R14" t="n">
-        <v>7328220</v>
+        <v>7328222</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,19 +2084,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,12 +2101,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2097,32 +2117,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135357247</v>
+        <v>135358233</v>
       </c>
       <c r="B15" t="n">
-        <v>80500</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>658109</v>
+        <v>658108</v>
       </c>
       <c r="R15" t="n">
-        <v>7328220</v>
+        <v>7328200</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2165,19 +2185,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,12 +2202,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2208,32 +2218,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135357256</v>
+        <v>135358234</v>
       </c>
       <c r="B16" t="n">
-        <v>97435</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658015</v>
+        <v>658060</v>
       </c>
       <c r="R16" t="n">
-        <v>7328371</v>
+        <v>7328226</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,19 +2286,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,12 +2303,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2319,32 +2319,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135356943</v>
+        <v>135358877</v>
       </c>
       <c r="B17" t="n">
-        <v>89354</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658013</v>
+        <v>658084</v>
       </c>
       <c r="R17" t="n">
-        <v>7328309</v>
+        <v>7328255</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,12 +2414,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2430,10 +2430,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135356953</v>
+        <v>135356934</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>83358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658084</v>
+        <v>658125</v>
       </c>
       <c r="R18" t="n">
-        <v>7328414</v>
+        <v>7328199</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135357254</v>
+        <v>135357244</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>658009</v>
+        <v>658102</v>
       </c>
       <c r="R19" t="n">
-        <v>7328373</v>
+        <v>7328232</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,32 +2652,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135357258</v>
+        <v>135358890</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>80493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657969</v>
+        <v>658030</v>
       </c>
       <c r="R20" t="n">
-        <v>7328406</v>
+        <v>7328251</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,12 +2747,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2763,32 +2763,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135357261</v>
+        <v>135357249</v>
       </c>
       <c r="B21" t="n">
-        <v>92245</v>
+        <v>80499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>657939</v>
+        <v>658109</v>
       </c>
       <c r="R21" t="n">
-        <v>7328422</v>
+        <v>7328220</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,32 +2874,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135356944</v>
+        <v>135357247</v>
       </c>
       <c r="B22" t="n">
-        <v>79452</v>
+        <v>80500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658000</v>
+        <v>658109</v>
       </c>
       <c r="R22" t="n">
-        <v>7328356</v>
+        <v>7328220</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,12 +2969,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2985,48 +2985,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135312324</v>
+        <v>135358889</v>
       </c>
       <c r="B23" t="n">
-        <v>91970</v>
+        <v>80500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Granliden, Granliden, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>657559</v>
+        <v>658030</v>
       </c>
       <c r="R23" t="n">
-        <v>7328362</v>
+        <v>7328251</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,12 +3050,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3070,44 +3080,48 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135357255</v>
+        <v>135358925</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>92593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>658009</v>
+        <v>657781</v>
       </c>
       <c r="R24" t="n">
-        <v>7328373</v>
+        <v>7328318</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3152,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3177,12 +3191,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3193,32 +3207,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135356949</v>
+        <v>135357256</v>
       </c>
       <c r="B25" t="n">
-        <v>91988</v>
+        <v>97435</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3231,10 +3245,10 @@
         <v>658015</v>
       </c>
       <c r="R25" t="n">
-        <v>7328401</v>
+        <v>7328371</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,7 +3277,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3287,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,12 +3302,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3304,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135357252</v>
+        <v>135356943</v>
       </c>
       <c r="B26" t="n">
-        <v>83222</v>
+        <v>89354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,21 +3329,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3339,13 +3353,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>658041</v>
+        <v>658013</v>
       </c>
       <c r="R26" t="n">
-        <v>7328283</v>
+        <v>7328309</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,7 +3388,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3384,7 +3398,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,12 +3413,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3415,32 +3429,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135356945</v>
+        <v>135356953</v>
       </c>
       <c r="B27" t="n">
-        <v>91937</v>
+        <v>92245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3450,13 +3464,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>657999</v>
+        <v>658084</v>
       </c>
       <c r="R27" t="n">
-        <v>7328359</v>
+        <v>7328414</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3485,7 +3499,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3509,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,32 +3540,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135356947</v>
+        <v>135357254</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>92245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,13 +3575,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>657973</v>
+        <v>658009</v>
       </c>
       <c r="R28" t="n">
-        <v>7328369</v>
+        <v>7328373</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3596,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3606,7 +3620,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,12 +3635,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3637,32 +3651,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135356936</v>
+        <v>135357258</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3672,10 +3686,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>658123</v>
+        <v>657969</v>
       </c>
       <c r="R29" t="n">
-        <v>7328269</v>
+        <v>7328406</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3707,7 +3721,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3717,7 +3731,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,12 +3746,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3748,32 +3762,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135356938</v>
+        <v>135357261</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3783,10 +3797,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>658123</v>
+        <v>657939</v>
       </c>
       <c r="R30" t="n">
-        <v>7328290</v>
+        <v>7328422</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3818,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3828,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,12 +3857,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3859,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135356939</v>
+        <v>135358870</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3894,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>658104</v>
+        <v>658077</v>
       </c>
       <c r="R31" t="n">
-        <v>7328291</v>
+        <v>7328269</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3954,12 +3968,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3970,32 +3984,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135356940</v>
+        <v>135358879</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4005,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>658075</v>
+        <v>658081</v>
       </c>
       <c r="R32" t="n">
-        <v>7328297</v>
+        <v>7328266</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4040,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4050,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4065,12 +4079,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4081,32 +4095,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135356941</v>
+        <v>135358923</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>92245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4116,13 +4130,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>658052</v>
+        <v>657772</v>
       </c>
       <c r="R33" t="n">
-        <v>7328288</v>
+        <v>7328324</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4151,7 +4165,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4161,7 +4175,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4176,12 +4190,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4192,32 +4206,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135356946</v>
+        <v>135356944</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4227,13 +4241,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>657993</v>
+        <v>658000</v>
       </c>
       <c r="R34" t="n">
-        <v>7328349</v>
+        <v>7328356</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4262,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4272,7 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,32 +4317,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135356948</v>
+        <v>135358859</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4338,13 +4352,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>658007</v>
+        <v>658186</v>
       </c>
       <c r="R35" t="n">
-        <v>7328388</v>
+        <v>7328274</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4373,7 +4387,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4383,7 +4397,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4398,12 +4412,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4414,32 +4428,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135356951</v>
+        <v>135358869</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4449,13 +4463,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>658045</v>
+        <v>658111</v>
       </c>
       <c r="R36" t="n">
-        <v>7328393</v>
+        <v>7328284</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4484,7 +4498,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4494,7 +4508,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,12 +4523,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4525,32 +4539,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135356952</v>
+        <v>135358887</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4560,13 +4574,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>658067</v>
+        <v>658030</v>
       </c>
       <c r="R37" t="n">
-        <v>7328396</v>
+        <v>7328257</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4595,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4605,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4620,12 +4634,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4636,32 +4650,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135357250</v>
+        <v>135358906</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4671,10 +4685,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>658064</v>
+        <v>658011</v>
       </c>
       <c r="R38" t="n">
-        <v>7328265</v>
+        <v>7328275</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4706,7 +4720,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4716,7 +4730,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4731,12 +4745,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4747,32 +4761,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135357251</v>
+        <v>135358908</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4782,10 +4796,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>658041</v>
+        <v>657974</v>
       </c>
       <c r="R39" t="n">
-        <v>7328283</v>
+        <v>7328291</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4817,7 +4831,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4827,7 +4841,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4842,12 +4856,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4858,32 +4872,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135357253</v>
+        <v>135358915</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4907,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657993</v>
+        <v>657914</v>
       </c>
       <c r="R40" t="n">
-        <v>7328350</v>
+        <v>7328307</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4928,7 +4942,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4952,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4953,12 +4967,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4969,32 +4983,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135357259</v>
+        <v>135358917</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5004,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657958</v>
+        <v>657893</v>
       </c>
       <c r="R41" t="n">
-        <v>7328432</v>
+        <v>7328286</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5039,7 +5053,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5049,7 +5063,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5064,12 +5078,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5080,48 +5094,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135357262</v>
+        <v>135312324</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>91970</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Granliden, Granliden, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657758</v>
+        <v>657559</v>
       </c>
       <c r="R42" t="n">
-        <v>7328354</v>
+        <v>7328362</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5145,22 +5159,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5175,26 +5179,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135356935</v>
+        <v>135357255</v>
       </c>
       <c r="B43" t="n">
-        <v>83358</v>
+        <v>91974</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,13 +5226,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>658122</v>
+        <v>658009</v>
       </c>
       <c r="R43" t="n">
-        <v>7328267</v>
+        <v>7328373</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5286,12 +5286,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135356950</v>
+        <v>135358867</v>
       </c>
       <c r="B44" t="n">
-        <v>83358</v>
+        <v>91974</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,21 +5313,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>658045</v>
+        <v>658115</v>
       </c>
       <c r="R44" t="n">
-        <v>7328393</v>
+        <v>7328284</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,12 +5397,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5413,57 +5413,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135357260</v>
+        <v>135358919</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>91974</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657949</v>
+        <v>657901</v>
       </c>
       <c r="R45" t="n">
-        <v>7328433</v>
+        <v>7328279</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5495,7 +5483,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5505,12 +5493,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5519,19 +5502,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5542,32 +5524,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135357257</v>
+        <v>135358922</v>
       </c>
       <c r="B46" t="n">
-        <v>99217</v>
+        <v>91974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5577,10 +5559,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>657988</v>
+        <v>657772</v>
       </c>
       <c r="R46" t="n">
-        <v>7328384</v>
+        <v>7328324</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5612,7 +5594,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5622,7 +5604,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5619,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5653,10 +5635,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135358229</v>
+        <v>135356949</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>91988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,21 +5646,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5688,13 +5670,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>658194</v>
+        <v>658015</v>
       </c>
       <c r="R47" t="n">
-        <v>7328255</v>
+        <v>7328401</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5721,9 +5703,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5738,12 +5730,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5754,32 +5746,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135358230</v>
+        <v>135357252</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5789,13 +5781,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>658217</v>
+        <v>658041</v>
       </c>
       <c r="R48" t="n">
-        <v>7328285</v>
+        <v>7328283</v>
       </c>
       <c r="S48" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5822,9 +5814,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5839,15 +5841,6022 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135358860</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>658151</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7328266</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135358872</v>
+      </c>
+      <c r="B50" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>658075</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7328261</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135358902</v>
+      </c>
+      <c r="B51" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7328280</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135358911</v>
+      </c>
+      <c r="B52" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>657974</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7328302</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135358913</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>657911</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7328307</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135356945</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>657999</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7328359</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135356947</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>657973</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7328369</v>
+      </c>
+      <c r="S55" t="n">
+        <v>8</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135356936</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>658123</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7328269</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135356938</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>658123</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7328290</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135356939</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>658104</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7328291</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135356940</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>658075</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7328297</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135356941</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>658052</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7328288</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135356946</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>657993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7328349</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135356948</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>658007</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7328388</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135356951</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>658045</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7328393</v>
+      </c>
+      <c r="S63" t="n">
+        <v>9</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135356952</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>658067</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7328396</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135357250</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>658064</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7328265</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135357251</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>658041</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135357253</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>657993</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7328350</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135357259</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>657958</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7328432</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135357262</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>657758</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7328354</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135358861</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>658151</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7328266</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135358866</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>658124</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7328278</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135358871</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>658080</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7328268</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135358904</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7328280</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135358909</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>657975</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7328291</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135358912</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>657974</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7328302</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135358914</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>657914</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7328308</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135358918</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>657896</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7328293</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135358924</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>657769</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7328319</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135358910</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>657974</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7328303</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135356935</v>
+      </c>
+      <c r="B80" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>658122</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7328267</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135356950</v>
+      </c>
+      <c r="B81" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>658045</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7328393</v>
+      </c>
+      <c r="S81" t="n">
+        <v>9</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135358862</v>
+      </c>
+      <c r="B82" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>658142</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7328263</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135358896</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>658008</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7328268</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135358898</v>
+      </c>
+      <c r="B84" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>658006</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7328269</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135358894</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>658009</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7328269</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135358868</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>658107</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7328286</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135358892</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>658011</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7328274</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135358865</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>658125</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7328274</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135358873</v>
+      </c>
+      <c r="B89" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>658080</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7328262</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135358916</v>
+      </c>
+      <c r="B90" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>657914</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7328307</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135358921</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>657875</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7328357</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135358864</v>
+      </c>
+      <c r="B92" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>658134</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7328300</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135357260</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>657949</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7328433</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135357257</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>657988</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7328384</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135358927</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>657781</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7328332</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135358926</v>
+      </c>
+      <c r="B96" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>657781</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7328326</v>
+      </c>
+      <c r="S96" t="n">
+        <v>14</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135358920</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>657852</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7328299</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135358863</v>
+      </c>
+      <c r="B98" t="n">
+        <v>95840</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>658147</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7328286</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>135358229</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>658194</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7328255</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
           <t>Helen Sterner</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>Helen Sterner</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr">
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135358230</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>658217</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7328285</v>
+      </c>
+      <c r="S100" t="n">
+        <v>14</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135358858</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>658204</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7328271</v>
+      </c>
+      <c r="S101" t="n">
+        <v>29</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3873,7 +3873,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135358870</v>
+        <v>135358539</v>
       </c>
       <c r="B31" t="n">
         <v>92245</v>
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>658077</v>
+        <v>657750</v>
       </c>
       <c r="R31" t="n">
-        <v>7328269</v>
+        <v>7328363</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,12 +3968,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3984,7 +3984,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135358879</v>
+        <v>135358870</v>
       </c>
       <c r="B32" t="n">
         <v>92245</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>658081</v>
+        <v>658077</v>
       </c>
       <c r="R32" t="n">
-        <v>7328266</v>
+        <v>7328269</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4095,7 +4095,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135358923</v>
+        <v>135358879</v>
       </c>
       <c r="B33" t="n">
         <v>92245</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>657772</v>
+        <v>658081</v>
       </c>
       <c r="R33" t="n">
-        <v>7328324</v>
+        <v>7328266</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135356944</v>
+        <v>135358923</v>
       </c>
       <c r="B34" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>658000</v>
+        <v>657772</v>
       </c>
       <c r="R34" t="n">
-        <v>7328356</v>
+        <v>7328324</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4301,12 +4301,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4317,7 +4317,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135358859</v>
+        <v>135356944</v>
       </c>
       <c r="B35" t="n">
         <v>79452</v>
@@ -4352,13 +4352,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>658186</v>
+        <v>658000</v>
       </c>
       <c r="R35" t="n">
-        <v>7328274</v>
+        <v>7328356</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,12 +4412,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4428,7 +4428,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135358869</v>
+        <v>135358523</v>
       </c>
       <c r="B36" t="n">
         <v>79452</v>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>658111</v>
+        <v>658026</v>
       </c>
       <c r="R36" t="n">
-        <v>7328284</v>
+        <v>7328298</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4523,12 +4523,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4539,7 +4539,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135358887</v>
+        <v>135358526</v>
       </c>
       <c r="B37" t="n">
         <v>79452</v>
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>658030</v>
+        <v>657979</v>
       </c>
       <c r="R37" t="n">
-        <v>7328257</v>
+        <v>7328313</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,12 +4634,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4650,7 +4650,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135358906</v>
+        <v>135358531</v>
       </c>
       <c r="B38" t="n">
         <v>79452</v>
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>658011</v>
+        <v>657938</v>
       </c>
       <c r="R38" t="n">
-        <v>7328275</v>
+        <v>7328318</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,12 +4745,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4761,7 +4761,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135358908</v>
+        <v>135358534</v>
       </c>
       <c r="B39" t="n">
         <v>79452</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>657974</v>
+        <v>657814</v>
       </c>
       <c r="R39" t="n">
-        <v>7328291</v>
+        <v>7328378</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4872,7 +4872,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135358915</v>
+        <v>135358859</v>
       </c>
       <c r="B40" t="n">
         <v>79452</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657914</v>
+        <v>658186</v>
       </c>
       <c r="R40" t="n">
-        <v>7328307</v>
+        <v>7328274</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135358917</v>
+        <v>135358869</v>
       </c>
       <c r="B41" t="n">
         <v>79452</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657893</v>
+        <v>658111</v>
       </c>
       <c r="R41" t="n">
-        <v>7328286</v>
+        <v>7328284</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135312324</v>
+        <v>135358887</v>
       </c>
       <c r="B42" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,37 +5105,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Granliden, Granliden, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657559</v>
+        <v>658030</v>
       </c>
       <c r="R42" t="n">
-        <v>7328362</v>
+        <v>7328257</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5159,12 +5159,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5179,22 +5189,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135357255</v>
+        <v>135358906</v>
       </c>
       <c r="B43" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5216,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>658009</v>
+        <v>658011</v>
       </c>
       <c r="R43" t="n">
-        <v>7328373</v>
+        <v>7328275</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5261,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5285,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5286,12 +5300,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5302,10 +5316,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135358867</v>
+        <v>135358908</v>
       </c>
       <c r="B44" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,21 +5327,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5337,10 +5351,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>658115</v>
+        <v>657974</v>
       </c>
       <c r="R44" t="n">
-        <v>7328284</v>
+        <v>7328291</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5372,7 +5386,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5382,7 +5396,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,7 +5416,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5413,10 +5427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135358919</v>
+        <v>135358915</v>
       </c>
       <c r="B45" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5424,21 +5438,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5448,10 +5462,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657901</v>
+        <v>657914</v>
       </c>
       <c r="R45" t="n">
-        <v>7328279</v>
+        <v>7328307</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5483,7 +5497,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5493,7 +5507,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5513,7 +5527,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5524,10 +5538,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135358922</v>
+        <v>135358917</v>
       </c>
       <c r="B46" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5535,21 +5549,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5559,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>657772</v>
+        <v>657893</v>
       </c>
       <c r="R46" t="n">
-        <v>7328324</v>
+        <v>7328286</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5594,7 +5608,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5604,7 +5618,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,7 +5638,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5635,48 +5649,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135356949</v>
+        <v>135312324</v>
       </c>
       <c r="B47" t="n">
-        <v>91988</v>
+        <v>91970</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Granliden, Granliden, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>658015</v>
+        <v>657559</v>
       </c>
       <c r="R47" t="n">
-        <v>7328401</v>
+        <v>7328362</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5700,22 +5714,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5730,26 +5734,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135357252</v>
+        <v>135357255</v>
       </c>
       <c r="B48" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>658041</v>
+        <v>658009</v>
       </c>
       <c r="R48" t="n">
-        <v>7328283</v>
+        <v>7328373</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5857,10 +5857,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135358860</v>
+        <v>135358867</v>
       </c>
       <c r="B49" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5868,21 +5868,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>658151</v>
+        <v>658115</v>
       </c>
       <c r="R49" t="n">
-        <v>7328266</v>
+        <v>7328284</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135358872</v>
+        <v>135358919</v>
       </c>
       <c r="B50" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6003,13 +6003,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>658075</v>
+        <v>657901</v>
       </c>
       <c r="R50" t="n">
-        <v>7328261</v>
+        <v>7328279</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6048,12 +6048,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6073,7 +6068,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6084,10 +6079,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135358902</v>
+        <v>135358922</v>
       </c>
       <c r="B51" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,21 +6090,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6119,10 +6114,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>658009</v>
+        <v>657772</v>
       </c>
       <c r="R51" t="n">
-        <v>7328280</v>
+        <v>7328324</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6154,7 +6149,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6164,7 +6159,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6184,7 +6179,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6195,32 +6190,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135358911</v>
+        <v>135356949</v>
       </c>
       <c r="B52" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6230,13 +6225,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657974</v>
+        <v>658015</v>
       </c>
       <c r="R52" t="n">
-        <v>7328302</v>
+        <v>7328401</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6265,7 +6260,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6275,7 +6270,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6290,12 +6285,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6306,7 +6301,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135358913</v>
+        <v>135357252</v>
       </c>
       <c r="B53" t="n">
         <v>83222</v>
@@ -6341,13 +6336,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657911</v>
+        <v>658041</v>
       </c>
       <c r="R53" t="n">
-        <v>7328307</v>
+        <v>7328283</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6376,7 +6371,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6386,7 +6381,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6401,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6417,32 +6412,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135356945</v>
+        <v>135358860</v>
       </c>
       <c r="B54" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6452,13 +6447,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657999</v>
+        <v>658151</v>
       </c>
       <c r="R54" t="n">
-        <v>7328359</v>
+        <v>7328266</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6487,7 +6482,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6497,7 +6492,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6512,12 +6507,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6528,32 +6523,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135356947</v>
+        <v>135358872</v>
       </c>
       <c r="B55" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6563,13 +6558,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657973</v>
+        <v>658075</v>
       </c>
       <c r="R55" t="n">
-        <v>7328369</v>
+        <v>7328261</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6598,7 +6593,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6608,7 +6603,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6623,12 +6623,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6639,32 +6639,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135356936</v>
+        <v>135358902</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>658123</v>
+        <v>658009</v>
       </c>
       <c r="R56" t="n">
-        <v>7328269</v>
+        <v>7328280</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6734,12 +6734,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6750,32 +6750,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135356938</v>
+        <v>135358911</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6785,13 +6785,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>658123</v>
+        <v>657974</v>
       </c>
       <c r="R57" t="n">
-        <v>7328290</v>
+        <v>7328302</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6845,12 +6845,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6861,32 +6861,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135356939</v>
+        <v>135358913</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6896,13 +6896,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>658104</v>
+        <v>657911</v>
       </c>
       <c r="R58" t="n">
-        <v>7328291</v>
+        <v>7328307</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,12 +6956,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6972,32 +6972,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135356940</v>
+        <v>135356945</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>658075</v>
+        <v>657999</v>
       </c>
       <c r="R59" t="n">
-        <v>7328297</v>
+        <v>7328359</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,32 +7083,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135356941</v>
+        <v>135356947</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7118,13 +7118,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>658052</v>
+        <v>657973</v>
       </c>
       <c r="R60" t="n">
-        <v>7328288</v>
+        <v>7328369</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7194,7 +7194,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135356946</v>
+        <v>135356936</v>
       </c>
       <c r="B61" t="n">
         <v>79373</v>
@@ -7229,13 +7229,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>657993</v>
+        <v>658123</v>
       </c>
       <c r="R61" t="n">
-        <v>7328349</v>
+        <v>7328269</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7305,7 +7305,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356948</v>
+        <v>135356938</v>
       </c>
       <c r="B62" t="n">
         <v>79373</v>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>658007</v>
+        <v>658123</v>
       </c>
       <c r="R62" t="n">
-        <v>7328388</v>
+        <v>7328290</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7416,7 +7416,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135356951</v>
+        <v>135356939</v>
       </c>
       <c r="B63" t="n">
         <v>79373</v>
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>658045</v>
+        <v>658104</v>
       </c>
       <c r="R63" t="n">
-        <v>7328393</v>
+        <v>7328291</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7527,7 +7527,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135356952</v>
+        <v>135356940</v>
       </c>
       <c r="B64" t="n">
         <v>79373</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>658067</v>
+        <v>658075</v>
       </c>
       <c r="R64" t="n">
-        <v>7328396</v>
+        <v>7328297</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7638,7 +7638,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135357250</v>
+        <v>135356941</v>
       </c>
       <c r="B65" t="n">
         <v>79373</v>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>658064</v>
+        <v>658052</v>
       </c>
       <c r="R65" t="n">
-        <v>7328265</v>
+        <v>7328288</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7733,12 +7733,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7749,7 +7749,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135357251</v>
+        <v>135356946</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7784,13 +7784,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>658041</v>
+        <v>657993</v>
       </c>
       <c r="R66" t="n">
-        <v>7328283</v>
+        <v>7328349</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7844,12 +7844,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7860,7 +7860,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135357253</v>
+        <v>135356948</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>657993</v>
+        <v>658007</v>
       </c>
       <c r="R67" t="n">
-        <v>7328350</v>
+        <v>7328388</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7955,12 +7955,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7971,7 +7971,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135357259</v>
+        <v>135356951</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>657958</v>
+        <v>658045</v>
       </c>
       <c r="R68" t="n">
-        <v>7328432</v>
+        <v>7328393</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8066,12 +8066,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8082,7 +8082,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135357262</v>
+        <v>135356952</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -8117,13 +8117,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>657758</v>
+        <v>658067</v>
       </c>
       <c r="R69" t="n">
-        <v>7328354</v>
+        <v>7328396</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8177,12 +8177,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8193,7 +8193,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135358861</v>
+        <v>135357250</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>658151</v>
+        <v>658064</v>
       </c>
       <c r="R70" t="n">
-        <v>7328266</v>
+        <v>7328265</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8288,12 +8288,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8304,7 +8304,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135358866</v>
+        <v>135357251</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>658124</v>
+        <v>658041</v>
       </c>
       <c r="R71" t="n">
-        <v>7328278</v>
+        <v>7328283</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8399,12 +8399,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8415,7 +8415,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135358871</v>
+        <v>135357253</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>658080</v>
+        <v>657993</v>
       </c>
       <c r="R72" t="n">
-        <v>7328268</v>
+        <v>7328350</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,12 +8510,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135358904</v>
+        <v>135357259</v>
       </c>
       <c r="B73" t="n">
         <v>79373</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>658009</v>
+        <v>657958</v>
       </c>
       <c r="R73" t="n">
-        <v>7328280</v>
+        <v>7328432</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8621,12 +8621,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135358909</v>
+        <v>135357262</v>
       </c>
       <c r="B74" t="n">
         <v>79373</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657975</v>
+        <v>657758</v>
       </c>
       <c r="R74" t="n">
-        <v>7328291</v>
+        <v>7328354</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8732,12 +8732,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135358912</v>
+        <v>135358515</v>
       </c>
       <c r="B75" t="n">
         <v>79373</v>
@@ -8783,13 +8783,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657974</v>
+        <v>658143</v>
       </c>
       <c r="R75" t="n">
-        <v>7328302</v>
+        <v>7328264</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8859,7 +8859,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135358914</v>
+        <v>135358519</v>
       </c>
       <c r="B76" t="n">
         <v>79373</v>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>657914</v>
+        <v>658102</v>
       </c>
       <c r="R76" t="n">
-        <v>7328308</v>
+        <v>7328301</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8954,12 +8954,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8970,7 +8970,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135358918</v>
+        <v>135358521</v>
       </c>
       <c r="B77" t="n">
         <v>79373</v>
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>657896</v>
+        <v>658050</v>
       </c>
       <c r="R77" t="n">
-        <v>7328293</v>
+        <v>7328312</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9050,7 +9050,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9065,12 +9070,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9081,7 +9086,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135358924</v>
+        <v>135358525</v>
       </c>
       <c r="B78" t="n">
         <v>79373</v>
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657769</v>
+        <v>657982</v>
       </c>
       <c r="R78" t="n">
-        <v>7328319</v>
+        <v>7328312</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9151,7 +9156,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9161,7 +9166,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9176,12 +9181,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9192,32 +9197,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135358910</v>
+        <v>135358532</v>
       </c>
       <c r="B79" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9227,13 +9232,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657974</v>
+        <v>657854</v>
       </c>
       <c r="R79" t="n">
-        <v>7328303</v>
+        <v>7328329</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9262,7 +9267,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9272,7 +9277,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9287,12 +9292,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9303,32 +9308,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135356935</v>
+        <v>135358533</v>
       </c>
       <c r="B80" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9338,13 +9343,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>658122</v>
+        <v>657843</v>
       </c>
       <c r="R80" t="n">
-        <v>7328267</v>
+        <v>7328352</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9373,7 +9378,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9383,7 +9388,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9398,12 +9403,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9414,32 +9419,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135356950</v>
+        <v>135358536</v>
       </c>
       <c r="B81" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9449,13 +9454,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>658045</v>
+        <v>657778</v>
       </c>
       <c r="R81" t="n">
-        <v>7328393</v>
+        <v>7328385</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9484,7 +9489,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9494,7 +9499,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9509,12 +9514,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9525,32 +9530,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135358862</v>
+        <v>135358538</v>
       </c>
       <c r="B82" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9560,13 +9565,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>658142</v>
+        <v>657756</v>
       </c>
       <c r="R82" t="n">
-        <v>7328263</v>
+        <v>7328370</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9595,7 +9600,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9605,7 +9610,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9620,12 +9625,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9636,32 +9641,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135358896</v>
+        <v>135358861</v>
       </c>
       <c r="B83" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9671,10 +9676,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>658008</v>
+        <v>658151</v>
       </c>
       <c r="R83" t="n">
-        <v>7328268</v>
+        <v>7328266</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9706,7 +9711,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9716,7 +9721,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9736,7 +9741,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9747,32 +9752,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135358898</v>
+        <v>135358866</v>
       </c>
       <c r="B84" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9782,10 +9787,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>658006</v>
+        <v>658124</v>
       </c>
       <c r="R84" t="n">
-        <v>7328269</v>
+        <v>7328278</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9817,7 +9822,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9827,7 +9832,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9847,7 +9852,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9858,27 +9863,27 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135358894</v>
+        <v>135358871</v>
       </c>
       <c r="B85" t="n">
-        <v>80499</v>
+        <v>79373</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9893,10 +9898,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>658009</v>
+        <v>658080</v>
       </c>
       <c r="R85" t="n">
-        <v>7328269</v>
+        <v>7328268</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9928,7 +9933,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9938,7 +9943,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9958,7 +9963,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9969,32 +9974,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135358868</v>
+        <v>135358904</v>
       </c>
       <c r="B86" t="n">
-        <v>80500</v>
+        <v>79373</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>658107</v>
+        <v>658009</v>
       </c>
       <c r="R86" t="n">
-        <v>7328286</v>
+        <v>7328280</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10039,7 +10044,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10049,7 +10054,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10069,7 +10074,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10080,32 +10085,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135358892</v>
+        <v>135358909</v>
       </c>
       <c r="B87" t="n">
-        <v>80500</v>
+        <v>79373</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10115,13 +10120,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>658011</v>
+        <v>657975</v>
       </c>
       <c r="R87" t="n">
-        <v>7328274</v>
+        <v>7328291</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10150,7 +10155,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10160,7 +10165,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10180,7 +10185,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10191,32 +10196,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135358865</v>
+        <v>135358912</v>
       </c>
       <c r="B88" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10226,13 +10231,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>658125</v>
+        <v>657974</v>
       </c>
       <c r="R88" t="n">
-        <v>7328274</v>
+        <v>7328302</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10261,7 +10266,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10271,12 +10276,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10307,32 +10307,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135358873</v>
+        <v>135358914</v>
       </c>
       <c r="B89" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>658080</v>
+        <v>657914</v>
       </c>
       <c r="R89" t="n">
-        <v>7328262</v>
+        <v>7328308</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10418,32 +10418,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135358916</v>
+        <v>135358918</v>
       </c>
       <c r="B90" t="n">
-        <v>58136</v>
+        <v>79373</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657914</v>
+        <v>657896</v>
       </c>
       <c r="R90" t="n">
-        <v>7328307</v>
+        <v>7328293</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10529,32 +10529,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135358921</v>
+        <v>135358924</v>
       </c>
       <c r="B91" t="n">
-        <v>58136</v>
+        <v>79373</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657875</v>
+        <v>657769</v>
       </c>
       <c r="R91" t="n">
-        <v>7328357</v>
+        <v>7328319</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10640,32 +10640,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135358864</v>
+        <v>135358910</v>
       </c>
       <c r="B92" t="n">
-        <v>5201</v>
+        <v>78776</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>105930</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>658134</v>
+        <v>657974</v>
       </c>
       <c r="R92" t="n">
-        <v>7328300</v>
+        <v>7328303</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10751,60 +10751,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135357260</v>
+        <v>135356935</v>
       </c>
       <c r="B93" t="n">
-        <v>99195</v>
+        <v>83358</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657949</v>
+        <v>658122</v>
       </c>
       <c r="R93" t="n">
-        <v>7328433</v>
+        <v>7328267</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10833,7 +10821,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10843,12 +10831,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10857,19 +10840,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10880,32 +10862,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135357257</v>
+        <v>135356950</v>
       </c>
       <c r="B94" t="n">
-        <v>99217</v>
+        <v>83358</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10915,13 +10897,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657988</v>
+        <v>658045</v>
       </c>
       <c r="R94" t="n">
-        <v>7328384</v>
+        <v>7328393</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10950,7 +10932,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10960,7 +10942,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10975,12 +10957,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10991,32 +10973,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135358927</v>
+        <v>135358862</v>
       </c>
       <c r="B95" t="n">
-        <v>99217</v>
+        <v>83358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11026,13 +11008,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657781</v>
+        <v>658142</v>
       </c>
       <c r="R95" t="n">
-        <v>7328332</v>
+        <v>7328263</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11061,7 +11043,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11071,7 +11053,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11091,7 +11073,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11102,10 +11084,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135358926</v>
+        <v>135358896</v>
       </c>
       <c r="B96" t="n">
-        <v>100806</v>
+        <v>80493</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11113,21 +11095,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222584</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11137,13 +11119,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657781</v>
+        <v>658008</v>
       </c>
       <c r="R96" t="n">
-        <v>7328326</v>
+        <v>7328268</v>
       </c>
       <c r="S96" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11172,7 +11154,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11182,7 +11164,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11202,7 +11184,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11213,32 +11195,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135358920</v>
+        <v>135358898</v>
       </c>
       <c r="B97" t="n">
-        <v>79963</v>
+        <v>80493</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11248,10 +11230,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657852</v>
+        <v>658006</v>
       </c>
       <c r="R97" t="n">
-        <v>7328299</v>
+        <v>7328269</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11283,7 +11265,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11293,7 +11275,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11313,7 +11295,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11324,10 +11306,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135358863</v>
+        <v>135358520</v>
       </c>
       <c r="B98" t="n">
-        <v>95840</v>
+        <v>80499</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11335,21 +11317,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1004672</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11359,13 +11341,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>658147</v>
+        <v>658099</v>
       </c>
       <c r="R98" t="n">
-        <v>7328286</v>
+        <v>7328289</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11394,7 +11376,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11404,7 +11386,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11419,12 +11401,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11435,27 +11417,27 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135358229</v>
+        <v>135358894</v>
       </c>
       <c r="B99" t="n">
-        <v>79373</v>
+        <v>80499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11470,10 +11452,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>658194</v>
+        <v>658009</v>
       </c>
       <c r="R99" t="n">
-        <v>7328255</v>
+        <v>7328269</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11503,9 +11485,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11520,12 +11512,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11536,32 +11528,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135358230</v>
+        <v>135358516</v>
       </c>
       <c r="B100" t="n">
-        <v>79373</v>
+        <v>80500</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11571,13 +11563,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>658217</v>
+        <v>658109</v>
       </c>
       <c r="R100" t="n">
-        <v>7328285</v>
+        <v>7328286</v>
       </c>
       <c r="S100" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11604,9 +11596,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>på låga</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11621,12 +11628,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11637,32 +11644,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358858</v>
+        <v>135358868</v>
       </c>
       <c r="B101" t="n">
-        <v>79373</v>
+        <v>80500</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11672,13 +11679,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>658204</v>
+        <v>658107</v>
       </c>
       <c r="R101" t="n">
-        <v>7328271</v>
+        <v>7328286</v>
       </c>
       <c r="S101" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11707,7 +11714,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11717,7 +11724,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11737,7 +11744,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11748,32 +11755,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358857</v>
+        <v>135358892</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11783,13 +11790,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>658192</v>
+        <v>658011</v>
       </c>
       <c r="R102" t="n">
-        <v>7328281</v>
+        <v>7328274</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11818,7 +11825,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11828,12 +11835,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11853,10 +11855,2132 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>135358865</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>658125</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7328274</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr">
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>135358873</v>
+      </c>
+      <c r="B104" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>658080</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7328262</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>135358530</v>
+      </c>
+      <c r="B105" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>657916</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7328337</v>
+      </c>
+      <c r="S105" t="n">
+        <v>8</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>135358916</v>
+      </c>
+      <c r="B106" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>657914</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7328307</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>135358921</v>
+      </c>
+      <c r="B107" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>657875</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7328357</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>135358529</v>
+      </c>
+      <c r="B108" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>657920</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7328326</v>
+      </c>
+      <c r="S108" t="n">
+        <v>6</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>3st</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>135358864</v>
+      </c>
+      <c r="B109" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>658134</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7328300</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>135357260</v>
+      </c>
+      <c r="B110" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>657949</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7328433</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>135358537</v>
+      </c>
+      <c r="B111" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>657761</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7328385</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>135358540</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>657728</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7328365</v>
+      </c>
+      <c r="S112" t="n">
+        <v>12</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>135357257</v>
+      </c>
+      <c r="B113" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>657988</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7328384</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>135358927</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>657781</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7328332</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>135358926</v>
+      </c>
+      <c r="B115" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>657781</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7328326</v>
+      </c>
+      <c r="S115" t="n">
+        <v>14</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>135358920</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>657852</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7328299</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>135358863</v>
+      </c>
+      <c r="B117" t="n">
+        <v>95840</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>658147</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7328286</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>135358229</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>658194</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7328255</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>135358230</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>658217</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7328285</v>
+      </c>
+      <c r="S119" t="n">
+        <v>14</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>135358858</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>658204</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7328271</v>
+      </c>
+      <c r="S120" t="n">
+        <v>29</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135356932</v>
+        <v>135358513</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>80489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>658170</v>
+        <v>658136</v>
       </c>
       <c r="R9" t="n">
-        <v>7328245</v>
+        <v>7328218</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,12 +1556,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1572,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135356933</v>
+        <v>135356932</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658134</v>
+        <v>658170</v>
       </c>
       <c r="R10" t="n">
-        <v>7328255</v>
+        <v>7328245</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135357242</v>
+        <v>135356933</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658183</v>
+        <v>658134</v>
       </c>
       <c r="R11" t="n">
-        <v>7328256</v>
+        <v>7328255</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,12 +1778,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1794,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135357243</v>
+        <v>135357242</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658141</v>
+        <v>658183</v>
       </c>
       <c r="R12" t="n">
-        <v>7328242</v>
+        <v>7328256</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,7 +1905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135357245</v>
+        <v>135357243</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658102</v>
+        <v>658141</v>
       </c>
       <c r="R13" t="n">
-        <v>7328232</v>
+        <v>7328242</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135358232</v>
+        <v>135357245</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658139</v>
+        <v>658102</v>
       </c>
       <c r="R14" t="n">
-        <v>7328222</v>
+        <v>7328232</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,9 +2084,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,12 +2111,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2117,7 +2127,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135358233</v>
+        <v>135358232</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2152,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>658108</v>
+        <v>658139</v>
       </c>
       <c r="R15" t="n">
-        <v>7328200</v>
+        <v>7328222</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2218,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135358234</v>
+        <v>135358233</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658060</v>
+        <v>658108</v>
       </c>
       <c r="R16" t="n">
-        <v>7328226</v>
+        <v>7328200</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2319,7 +2329,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135358877</v>
+        <v>135358234</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2354,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658084</v>
+        <v>658060</v>
       </c>
       <c r="R17" t="n">
-        <v>7328255</v>
+        <v>7328226</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,19 +2397,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,12 +2414,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2430,32 +2430,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135356934</v>
+        <v>135358509</v>
       </c>
       <c r="B18" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658125</v>
+        <v>658175</v>
       </c>
       <c r="R18" t="n">
-        <v>7328199</v>
+        <v>7328168</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2541,32 +2541,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135357244</v>
+        <v>135358510</v>
       </c>
       <c r="B19" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>658102</v>
+        <v>658151</v>
       </c>
       <c r="R19" t="n">
-        <v>7328232</v>
+        <v>7328173</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2636,12 +2636,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2652,32 +2652,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135358890</v>
+        <v>135358877</v>
       </c>
       <c r="B20" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>658030</v>
+        <v>658084</v>
       </c>
       <c r="R20" t="n">
-        <v>7328251</v>
+        <v>7328255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,32 +2763,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135357249</v>
+        <v>135356934</v>
       </c>
       <c r="B21" t="n">
-        <v>80499</v>
+        <v>83358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>658109</v>
+        <v>658125</v>
       </c>
       <c r="R21" t="n">
-        <v>7328220</v>
+        <v>7328199</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,12 +2858,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2874,32 +2874,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135357247</v>
+        <v>135357244</v>
       </c>
       <c r="B22" t="n">
-        <v>80500</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658109</v>
+        <v>658102</v>
       </c>
       <c r="R22" t="n">
-        <v>7328220</v>
+        <v>7328232</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135358889</v>
+        <v>135358512</v>
       </c>
       <c r="B23" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,21 +2996,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>658030</v>
+        <v>658144</v>
       </c>
       <c r="R23" t="n">
-        <v>7328251</v>
+        <v>7328184</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,12 +3080,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3096,32 +3096,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135358925</v>
+        <v>135358890</v>
       </c>
       <c r="B24" t="n">
-        <v>92593</v>
+        <v>80493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>657781</v>
+        <v>658030</v>
       </c>
       <c r="R24" t="n">
-        <v>7328318</v>
+        <v>7328251</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,32 +3207,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135357256</v>
+        <v>135357249</v>
       </c>
       <c r="B25" t="n">
-        <v>97435</v>
+        <v>80499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>658015</v>
+        <v>658109</v>
       </c>
       <c r="R25" t="n">
-        <v>7328371</v>
+        <v>7328220</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,32 +3318,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135356943</v>
+        <v>135357247</v>
       </c>
       <c r="B26" t="n">
-        <v>89354</v>
+        <v>80500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3353,13 +3353,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>658013</v>
+        <v>658109</v>
       </c>
       <c r="R26" t="n">
-        <v>7328309</v>
+        <v>7328220</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3413,12 +3413,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3429,32 +3429,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135356953</v>
+        <v>135358889</v>
       </c>
       <c r="B27" t="n">
-        <v>92245</v>
+        <v>80500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>658084</v>
+        <v>658030</v>
       </c>
       <c r="R27" t="n">
-        <v>7328414</v>
+        <v>7328251</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,12 +3524,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3540,32 +3540,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135357254</v>
+        <v>135358514</v>
       </c>
       <c r="B28" t="n">
-        <v>92245</v>
+        <v>106309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>658009</v>
+        <v>658129</v>
       </c>
       <c r="R28" t="n">
-        <v>7328373</v>
+        <v>7328219</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3635,12 +3635,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3651,32 +3651,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135357258</v>
+        <v>135358925</v>
       </c>
       <c r="B29" t="n">
-        <v>92245</v>
+        <v>92593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657969</v>
+        <v>657781</v>
       </c>
       <c r="R29" t="n">
-        <v>7328406</v>
+        <v>7328318</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,12 +3746,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135357261</v>
+        <v>135357256</v>
       </c>
       <c r="B30" t="n">
-        <v>92245</v>
+        <v>97435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,21 +3773,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657939</v>
+        <v>658015</v>
       </c>
       <c r="R30" t="n">
-        <v>7328422</v>
+        <v>7328371</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,10 +3873,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135358539</v>
+        <v>135356943</v>
       </c>
       <c r="B31" t="n">
-        <v>92245</v>
+        <v>89354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,21 +3884,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657750</v>
+        <v>658013</v>
       </c>
       <c r="R31" t="n">
-        <v>7328363</v>
+        <v>7328309</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,12 +3968,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3984,7 +3984,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135358870</v>
+        <v>135356953</v>
       </c>
       <c r="B32" t="n">
         <v>92245</v>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>658077</v>
+        <v>658084</v>
       </c>
       <c r="R32" t="n">
-        <v>7328269</v>
+        <v>7328414</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4079,12 +4079,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4095,7 +4095,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135358879</v>
+        <v>135357254</v>
       </c>
       <c r="B33" t="n">
         <v>92245</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>658081</v>
+        <v>658009</v>
       </c>
       <c r="R33" t="n">
-        <v>7328266</v>
+        <v>7328373</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,12 +4190,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135358923</v>
+        <v>135357258</v>
       </c>
       <c r="B34" t="n">
         <v>92245</v>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>657772</v>
+        <v>657969</v>
       </c>
       <c r="R34" t="n">
-        <v>7328324</v>
+        <v>7328406</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4301,12 +4301,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4317,10 +4317,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135356944</v>
+        <v>135357261</v>
       </c>
       <c r="B35" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,21 +4328,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4352,13 +4352,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>658000</v>
+        <v>657939</v>
       </c>
       <c r="R35" t="n">
-        <v>7328356</v>
+        <v>7328422</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,12 +4412,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4428,10 +4428,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135358523</v>
+        <v>135358539</v>
       </c>
       <c r="B36" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4439,21 +4439,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>658026</v>
+        <v>657750</v>
       </c>
       <c r="R36" t="n">
-        <v>7328298</v>
+        <v>7328363</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,10 +4539,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135358526</v>
+        <v>135358870</v>
       </c>
       <c r="B37" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4550,21 +4550,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>657979</v>
+        <v>658077</v>
       </c>
       <c r="R37" t="n">
-        <v>7328313</v>
+        <v>7328269</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,12 +4634,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4650,10 +4650,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135358531</v>
+        <v>135358879</v>
       </c>
       <c r="B38" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>657938</v>
+        <v>658081</v>
       </c>
       <c r="R38" t="n">
-        <v>7328318</v>
+        <v>7328266</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,12 +4745,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135358534</v>
+        <v>135358923</v>
       </c>
       <c r="B39" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>657814</v>
+        <v>657772</v>
       </c>
       <c r="R39" t="n">
-        <v>7328378</v>
+        <v>7328324</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4872,7 +4872,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135358859</v>
+        <v>135356944</v>
       </c>
       <c r="B40" t="n">
         <v>79452</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>658186</v>
+        <v>658000</v>
       </c>
       <c r="R40" t="n">
-        <v>7328274</v>
+        <v>7328356</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4967,12 +4967,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135358869</v>
+        <v>135358523</v>
       </c>
       <c r="B41" t="n">
         <v>79452</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>658111</v>
+        <v>658026</v>
       </c>
       <c r="R41" t="n">
-        <v>7328284</v>
+        <v>7328298</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,12 +5078,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5094,7 +5094,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135358887</v>
+        <v>135358526</v>
       </c>
       <c r="B42" t="n">
         <v>79452</v>
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>658030</v>
+        <v>657979</v>
       </c>
       <c r="R42" t="n">
-        <v>7328257</v>
+        <v>7328313</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,12 +5189,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5205,7 +5205,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135358906</v>
+        <v>135358531</v>
       </c>
       <c r="B43" t="n">
         <v>79452</v>
@@ -5240,13 +5240,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>658011</v>
+        <v>657938</v>
       </c>
       <c r="R43" t="n">
-        <v>7328275</v>
+        <v>7328318</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,12 +5300,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5316,7 +5316,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135358908</v>
+        <v>135358534</v>
       </c>
       <c r="B44" t="n">
         <v>79452</v>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657974</v>
+        <v>657814</v>
       </c>
       <c r="R44" t="n">
-        <v>7328291</v>
+        <v>7328378</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5411,12 +5411,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5427,7 +5427,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135358915</v>
+        <v>135358859</v>
       </c>
       <c r="B45" t="n">
         <v>79452</v>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657914</v>
+        <v>658186</v>
       </c>
       <c r="R45" t="n">
-        <v>7328307</v>
+        <v>7328274</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,7 +5538,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135358917</v>
+        <v>135358869</v>
       </c>
       <c r="B46" t="n">
         <v>79452</v>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>657893</v>
+        <v>658111</v>
       </c>
       <c r="R46" t="n">
-        <v>7328286</v>
+        <v>7328284</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5649,10 +5649,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135312324</v>
+        <v>135358887</v>
       </c>
       <c r="B47" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,37 +5660,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Granliden, Granliden, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>657559</v>
+        <v>658030</v>
       </c>
       <c r="R47" t="n">
-        <v>7328362</v>
+        <v>7328257</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5714,12 +5714,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5734,22 +5744,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135357255</v>
+        <v>135358906</v>
       </c>
       <c r="B48" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5757,21 +5771,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5781,10 +5795,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>658009</v>
+        <v>658011</v>
       </c>
       <c r="R48" t="n">
-        <v>7328373</v>
+        <v>7328275</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5816,7 +5830,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,7 +5840,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5841,12 +5855,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5857,10 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135358867</v>
+        <v>135358908</v>
       </c>
       <c r="B49" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5868,21 +5882,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5892,10 +5906,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>658115</v>
+        <v>657974</v>
       </c>
       <c r="R49" t="n">
-        <v>7328284</v>
+        <v>7328291</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5927,7 +5941,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5937,7 +5951,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5968,10 +5982,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135358919</v>
+        <v>135358915</v>
       </c>
       <c r="B50" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5979,21 +5993,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6003,10 +6017,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>657901</v>
+        <v>657914</v>
       </c>
       <c r="R50" t="n">
-        <v>7328279</v>
+        <v>7328307</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6038,7 +6052,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6048,7 +6062,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6079,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135358922</v>
+        <v>135358917</v>
       </c>
       <c r="B51" t="n">
-        <v>91974</v>
+        <v>79452</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6090,21 +6104,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6114,10 +6128,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657772</v>
+        <v>657893</v>
       </c>
       <c r="R51" t="n">
-        <v>7328324</v>
+        <v>7328286</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6149,7 +6163,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6159,7 +6173,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6190,48 +6204,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135356949</v>
+        <v>135312324</v>
       </c>
       <c r="B52" t="n">
-        <v>91988</v>
+        <v>91970</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Granliden, Granliden, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>658015</v>
+        <v>657559</v>
       </c>
       <c r="R52" t="n">
-        <v>7328401</v>
+        <v>7328362</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6255,22 +6269,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6285,26 +6289,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135357252</v>
+        <v>135357255</v>
       </c>
       <c r="B53" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6312,21 +6312,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>658041</v>
+        <v>658009</v>
       </c>
       <c r="R53" t="n">
-        <v>7328283</v>
+        <v>7328373</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6412,10 +6412,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135358860</v>
+        <v>135358867</v>
       </c>
       <c r="B54" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6423,21 +6423,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>658151</v>
+        <v>658115</v>
       </c>
       <c r="R54" t="n">
-        <v>7328266</v>
+        <v>7328284</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6523,10 +6523,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135358872</v>
+        <v>135358919</v>
       </c>
       <c r="B55" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,21 +6534,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6558,13 +6558,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>658075</v>
+        <v>657901</v>
       </c>
       <c r="R55" t="n">
-        <v>7328261</v>
+        <v>7328279</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6603,12 +6603,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6639,10 +6634,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135358902</v>
+        <v>135358922</v>
       </c>
       <c r="B56" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6650,21 +6645,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6674,10 +6669,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>658009</v>
+        <v>657772</v>
       </c>
       <c r="R56" t="n">
-        <v>7328280</v>
+        <v>7328324</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6709,7 +6704,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6719,7 +6714,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6750,32 +6745,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135358911</v>
+        <v>135356949</v>
       </c>
       <c r="B57" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6785,13 +6780,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657974</v>
+        <v>658015</v>
       </c>
       <c r="R57" t="n">
-        <v>7328302</v>
+        <v>7328401</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6820,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6830,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6845,12 +6840,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6861,7 +6856,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135358913</v>
+        <v>135357252</v>
       </c>
       <c r="B58" t="n">
         <v>83222</v>
@@ -6896,13 +6891,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>657911</v>
+        <v>658041</v>
       </c>
       <c r="R58" t="n">
-        <v>7328307</v>
+        <v>7328283</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6931,7 +6926,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6941,7 +6936,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,12 +6951,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6972,32 +6967,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135356945</v>
+        <v>135358860</v>
       </c>
       <c r="B59" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7007,13 +7002,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>657999</v>
+        <v>658151</v>
       </c>
       <c r="R59" t="n">
-        <v>7328359</v>
+        <v>7328266</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7042,7 +7037,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7052,7 +7047,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7067,12 +7062,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7083,32 +7078,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135356947</v>
+        <v>135358872</v>
       </c>
       <c r="B60" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7118,13 +7113,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>657973</v>
+        <v>658075</v>
       </c>
       <c r="R60" t="n">
-        <v>7328369</v>
+        <v>7328261</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7153,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7158,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7178,12 +7178,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135356936</v>
+        <v>135358902</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>658123</v>
+        <v>658009</v>
       </c>
       <c r="R61" t="n">
-        <v>7328269</v>
+        <v>7328280</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7289,12 +7289,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7305,32 +7305,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356938</v>
+        <v>135358911</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>658123</v>
+        <v>657974</v>
       </c>
       <c r="R62" t="n">
-        <v>7328290</v>
+        <v>7328302</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7400,12 +7400,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7416,32 +7416,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135356939</v>
+        <v>135358913</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>658104</v>
+        <v>657911</v>
       </c>
       <c r="R63" t="n">
-        <v>7328291</v>
+        <v>7328307</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7511,12 +7511,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7527,32 +7527,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135356940</v>
+        <v>135356945</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>658075</v>
+        <v>657999</v>
       </c>
       <c r="R64" t="n">
-        <v>7328297</v>
+        <v>7328359</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7638,32 +7638,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135356941</v>
+        <v>135356947</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>658052</v>
+        <v>657973</v>
       </c>
       <c r="R65" t="n">
-        <v>7328288</v>
+        <v>7328369</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7749,7 +7749,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135356946</v>
+        <v>135356936</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7784,13 +7784,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>657993</v>
+        <v>658123</v>
       </c>
       <c r="R66" t="n">
-        <v>7328349</v>
+        <v>7328269</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7860,7 +7860,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356948</v>
+        <v>135356938</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>658007</v>
+        <v>658123</v>
       </c>
       <c r="R67" t="n">
-        <v>7328388</v>
+        <v>7328290</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7971,7 +7971,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135356951</v>
+        <v>135356939</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>658045</v>
+        <v>658104</v>
       </c>
       <c r="R68" t="n">
-        <v>7328393</v>
+        <v>7328291</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8082,7 +8082,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135356952</v>
+        <v>135356940</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -8117,13 +8117,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>658067</v>
+        <v>658075</v>
       </c>
       <c r="R69" t="n">
-        <v>7328396</v>
+        <v>7328297</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8193,7 +8193,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135357250</v>
+        <v>135356941</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -8228,13 +8228,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>658064</v>
+        <v>658052</v>
       </c>
       <c r="R70" t="n">
-        <v>7328265</v>
+        <v>7328288</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8288,12 +8288,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8304,7 +8304,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135357251</v>
+        <v>135356946</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>658041</v>
+        <v>657993</v>
       </c>
       <c r="R71" t="n">
-        <v>7328283</v>
+        <v>7328349</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8399,12 +8399,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8415,7 +8415,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135357253</v>
+        <v>135356948</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>657993</v>
+        <v>658007</v>
       </c>
       <c r="R72" t="n">
-        <v>7328350</v>
+        <v>7328388</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,12 +8510,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135357259</v>
+        <v>135356951</v>
       </c>
       <c r="B73" t="n">
         <v>79373</v>
@@ -8561,13 +8561,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657958</v>
+        <v>658045</v>
       </c>
       <c r="R73" t="n">
-        <v>7328432</v>
+        <v>7328393</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135357262</v>
+        <v>135356952</v>
       </c>
       <c r="B74" t="n">
         <v>79373</v>
@@ -8672,13 +8672,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657758</v>
+        <v>658067</v>
       </c>
       <c r="R74" t="n">
-        <v>7328354</v>
+        <v>7328396</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8732,12 +8732,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135358515</v>
+        <v>135357250</v>
       </c>
       <c r="B75" t="n">
         <v>79373</v>
@@ -8783,13 +8783,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>658143</v>
+        <v>658064</v>
       </c>
       <c r="R75" t="n">
-        <v>7328264</v>
+        <v>7328265</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8859,7 +8859,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135358519</v>
+        <v>135357251</v>
       </c>
       <c r="B76" t="n">
         <v>79373</v>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>658102</v>
+        <v>658041</v>
       </c>
       <c r="R76" t="n">
-        <v>7328301</v>
+        <v>7328283</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8954,12 +8954,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8970,7 +8970,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135358521</v>
+        <v>135357253</v>
       </c>
       <c r="B77" t="n">
         <v>79373</v>
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>658050</v>
+        <v>657993</v>
       </c>
       <c r="R77" t="n">
-        <v>7328312</v>
+        <v>7328350</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9050,12 +9050,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>mycket</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9070,12 +9065,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9086,7 +9081,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135358525</v>
+        <v>135357259</v>
       </c>
       <c r="B78" t="n">
         <v>79373</v>
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657982</v>
+        <v>657958</v>
       </c>
       <c r="R78" t="n">
-        <v>7328312</v>
+        <v>7328432</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9156,7 +9151,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9166,7 +9161,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9181,12 +9176,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9197,7 +9192,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135358532</v>
+        <v>135357262</v>
       </c>
       <c r="B79" t="n">
         <v>79373</v>
@@ -9232,13 +9227,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657854</v>
+        <v>657758</v>
       </c>
       <c r="R79" t="n">
-        <v>7328329</v>
+        <v>7328354</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9267,7 +9262,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9277,7 +9272,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9292,12 +9287,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9308,7 +9303,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135358533</v>
+        <v>135358515</v>
       </c>
       <c r="B80" t="n">
         <v>79373</v>
@@ -9343,10 +9338,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657843</v>
+        <v>658143</v>
       </c>
       <c r="R80" t="n">
-        <v>7328352</v>
+        <v>7328264</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9378,7 +9373,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9388,7 +9383,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9419,7 +9414,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135358536</v>
+        <v>135358519</v>
       </c>
       <c r="B81" t="n">
         <v>79373</v>
@@ -9454,10 +9449,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>657778</v>
+        <v>658102</v>
       </c>
       <c r="R81" t="n">
-        <v>7328385</v>
+        <v>7328301</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9489,7 +9484,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9499,7 +9494,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9530,7 +9525,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135358538</v>
+        <v>135358521</v>
       </c>
       <c r="B82" t="n">
         <v>79373</v>
@@ -9565,13 +9560,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657756</v>
+        <v>658050</v>
       </c>
       <c r="R82" t="n">
-        <v>7328370</v>
+        <v>7328312</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9600,7 +9595,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9610,7 +9605,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9641,7 +9641,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135358861</v>
+        <v>135358525</v>
       </c>
       <c r="B83" t="n">
         <v>79373</v>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>658151</v>
+        <v>657982</v>
       </c>
       <c r="R83" t="n">
-        <v>7328266</v>
+        <v>7328312</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9736,12 +9736,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9752,7 +9752,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135358866</v>
+        <v>135358532</v>
       </c>
       <c r="B84" t="n">
         <v>79373</v>
@@ -9787,13 +9787,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>658124</v>
+        <v>657854</v>
       </c>
       <c r="R84" t="n">
-        <v>7328278</v>
+        <v>7328329</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9847,12 +9847,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9863,7 +9863,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135358871</v>
+        <v>135358533</v>
       </c>
       <c r="B85" t="n">
         <v>79373</v>
@@ -9898,13 +9898,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>658080</v>
+        <v>657843</v>
       </c>
       <c r="R85" t="n">
-        <v>7328268</v>
+        <v>7328352</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9958,12 +9958,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9974,7 +9974,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135358904</v>
+        <v>135358536</v>
       </c>
       <c r="B86" t="n">
         <v>79373</v>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>658009</v>
+        <v>657778</v>
       </c>
       <c r="R86" t="n">
-        <v>7328280</v>
+        <v>7328385</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10069,12 +10069,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10085,7 +10085,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135358909</v>
+        <v>135358538</v>
       </c>
       <c r="B87" t="n">
         <v>79373</v>
@@ -10120,13 +10120,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657975</v>
+        <v>657756</v>
       </c>
       <c r="R87" t="n">
-        <v>7328291</v>
+        <v>7328370</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10180,12 +10180,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10196,7 +10196,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135358912</v>
+        <v>135358861</v>
       </c>
       <c r="B88" t="n">
         <v>79373</v>
@@ -10231,13 +10231,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657974</v>
+        <v>658151</v>
       </c>
       <c r="R88" t="n">
-        <v>7328302</v>
+        <v>7328266</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10307,7 +10307,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135358914</v>
+        <v>135358866</v>
       </c>
       <c r="B89" t="n">
         <v>79373</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657914</v>
+        <v>658124</v>
       </c>
       <c r="R89" t="n">
-        <v>7328308</v>
+        <v>7328278</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135358918</v>
+        <v>135358871</v>
       </c>
       <c r="B90" t="n">
         <v>79373</v>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657896</v>
+        <v>658080</v>
       </c>
       <c r="R90" t="n">
-        <v>7328293</v>
+        <v>7328268</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10529,7 +10529,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135358924</v>
+        <v>135358904</v>
       </c>
       <c r="B91" t="n">
         <v>79373</v>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657769</v>
+        <v>658009</v>
       </c>
       <c r="R91" t="n">
-        <v>7328319</v>
+        <v>7328280</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10640,32 +10640,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135358910</v>
+        <v>135358909</v>
       </c>
       <c r="B92" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>657974</v>
+        <v>657975</v>
       </c>
       <c r="R92" t="n">
-        <v>7328303</v>
+        <v>7328291</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10751,32 +10751,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135356935</v>
+        <v>135358912</v>
       </c>
       <c r="B93" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>658122</v>
+        <v>657974</v>
       </c>
       <c r="R93" t="n">
-        <v>7328267</v>
+        <v>7328302</v>
       </c>
       <c r="S93" t="n">
         <v>6</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10846,12 +10846,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10862,32 +10862,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356950</v>
+        <v>135358914</v>
       </c>
       <c r="B94" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10897,13 +10897,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>658045</v>
+        <v>657914</v>
       </c>
       <c r="R94" t="n">
-        <v>7328393</v>
+        <v>7328308</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10957,12 +10957,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10973,32 +10973,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135358862</v>
+        <v>135358918</v>
       </c>
       <c r="B95" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>658142</v>
+        <v>657896</v>
       </c>
       <c r="R95" t="n">
-        <v>7328263</v>
+        <v>7328293</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11084,32 +11084,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135358896</v>
+        <v>135358924</v>
       </c>
       <c r="B96" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11119,10 +11119,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>658008</v>
+        <v>657769</v>
       </c>
       <c r="R96" t="n">
-        <v>7328268</v>
+        <v>7328319</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11195,32 +11195,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135358898</v>
+        <v>135358910</v>
       </c>
       <c r="B97" t="n">
-        <v>80493</v>
+        <v>78776</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>658006</v>
+        <v>657974</v>
       </c>
       <c r="R97" t="n">
-        <v>7328269</v>
+        <v>7328303</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11306,32 +11306,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135358520</v>
+        <v>135356935</v>
       </c>
       <c r="B98" t="n">
-        <v>80499</v>
+        <v>83358</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11341,13 +11341,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>658099</v>
+        <v>658122</v>
       </c>
       <c r="R98" t="n">
-        <v>7328289</v>
+        <v>7328267</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11401,12 +11401,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11417,32 +11417,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135358894</v>
+        <v>135356950</v>
       </c>
       <c r="B99" t="n">
-        <v>80499</v>
+        <v>83358</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>658009</v>
+        <v>658045</v>
       </c>
       <c r="R99" t="n">
-        <v>7328269</v>
+        <v>7328393</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11512,12 +11512,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11528,32 +11528,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135358516</v>
+        <v>135358862</v>
       </c>
       <c r="B100" t="n">
-        <v>80500</v>
+        <v>83358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11563,13 +11563,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>658109</v>
+        <v>658142</v>
       </c>
       <c r="R100" t="n">
-        <v>7328286</v>
+        <v>7328263</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11608,12 +11608,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>på låga</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11628,12 +11623,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11644,10 +11639,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358868</v>
+        <v>135358896</v>
       </c>
       <c r="B101" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11655,21 +11650,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11679,10 +11674,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>658107</v>
+        <v>658008</v>
       </c>
       <c r="R101" t="n">
-        <v>7328286</v>
+        <v>7328268</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11714,7 +11709,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11724,7 +11719,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11755,10 +11750,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358892</v>
+        <v>135358898</v>
       </c>
       <c r="B102" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11766,21 +11761,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11790,13 +11785,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>658011</v>
+        <v>658006</v>
       </c>
       <c r="R102" t="n">
-        <v>7328274</v>
+        <v>7328269</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11825,7 +11820,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11835,7 +11830,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11866,32 +11861,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358865</v>
+        <v>135358520</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>80499</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11901,13 +11896,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>658125</v>
+        <v>658099</v>
       </c>
       <c r="R103" t="n">
-        <v>7328274</v>
+        <v>7328289</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11936,7 +11931,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11946,12 +11941,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11966,12 +11956,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11982,10 +11972,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135358873</v>
+        <v>135358894</v>
       </c>
       <c r="B104" t="n">
-        <v>5181</v>
+        <v>80499</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11993,21 +11983,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12017,10 +12007,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>658080</v>
+        <v>658009</v>
       </c>
       <c r="R104" t="n">
-        <v>7328262</v>
+        <v>7328269</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12052,7 +12042,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12062,7 +12052,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12093,32 +12083,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135358530</v>
+        <v>135358516</v>
       </c>
       <c r="B105" t="n">
-        <v>58136</v>
+        <v>80500</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12128,13 +12118,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657916</v>
+        <v>658109</v>
       </c>
       <c r="R105" t="n">
-        <v>7328337</v>
+        <v>7328286</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12163,7 +12153,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12173,7 +12163,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>på låga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12204,32 +12199,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135358916</v>
+        <v>135358868</v>
       </c>
       <c r="B106" t="n">
-        <v>58136</v>
+        <v>80500</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12239,10 +12234,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657914</v>
+        <v>658107</v>
       </c>
       <c r="R106" t="n">
-        <v>7328307</v>
+        <v>7328286</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12274,7 +12269,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12284,7 +12279,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12315,32 +12310,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135358921</v>
+        <v>135358892</v>
       </c>
       <c r="B107" t="n">
-        <v>58136</v>
+        <v>80500</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12350,13 +12345,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657875</v>
+        <v>658011</v>
       </c>
       <c r="R107" t="n">
-        <v>7328357</v>
+        <v>7328274</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12385,7 +12380,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12395,7 +12390,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12426,10 +12421,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135358529</v>
+        <v>135358865</v>
       </c>
       <c r="B108" t="n">
-        <v>58079</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12437,16 +12432,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12461,13 +12456,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657920</v>
+        <v>658125</v>
       </c>
       <c r="R108" t="n">
-        <v>7328326</v>
+        <v>7328274</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12496,7 +12491,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12506,12 +12501,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12526,12 +12521,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12542,10 +12537,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135358864</v>
+        <v>135358873</v>
       </c>
       <c r="B109" t="n">
-        <v>5201</v>
+        <v>5181</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12553,21 +12548,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12577,13 +12572,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>658134</v>
+        <v>658080</v>
       </c>
       <c r="R109" t="n">
-        <v>7328300</v>
+        <v>7328262</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12612,7 +12607,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12622,7 +12617,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12653,60 +12648,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135357260</v>
+        <v>135358530</v>
       </c>
       <c r="B110" t="n">
-        <v>99195</v>
+        <v>58136</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>657949</v>
+        <v>657916</v>
       </c>
       <c r="R110" t="n">
-        <v>7328433</v>
+        <v>7328337</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12735,7 +12718,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12745,12 +12728,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12759,19 +12737,18 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12782,32 +12759,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135358537</v>
+        <v>135358916</v>
       </c>
       <c r="B111" t="n">
-        <v>106309</v>
+        <v>58136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221725</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12817,10 +12794,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657761</v>
+        <v>657914</v>
       </c>
       <c r="R111" t="n">
-        <v>7328385</v>
+        <v>7328307</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12852,7 +12829,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12862,7 +12839,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12877,12 +12854,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12893,32 +12870,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358540</v>
+        <v>135358921</v>
       </c>
       <c r="B112" t="n">
-        <v>98066</v>
+        <v>58136</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12928,13 +12905,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657728</v>
+        <v>657875</v>
       </c>
       <c r="R112" t="n">
-        <v>7328365</v>
+        <v>7328357</v>
       </c>
       <c r="S112" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12963,7 +12940,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12973,7 +12950,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12988,12 +12965,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13004,32 +12981,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135357257</v>
+        <v>135358529</v>
       </c>
       <c r="B113" t="n">
-        <v>99217</v>
+        <v>58079</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13039,13 +13016,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657988</v>
+        <v>657920</v>
       </c>
       <c r="R113" t="n">
-        <v>7328384</v>
+        <v>7328326</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13074,7 +13051,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13084,7 +13061,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13099,12 +13081,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13115,10 +13097,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135358927</v>
+        <v>135358864</v>
       </c>
       <c r="B114" t="n">
-        <v>99217</v>
+        <v>5201</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13126,21 +13108,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221952</v>
+        <v>105930</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13150,13 +13132,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657781</v>
+        <v>658134</v>
       </c>
       <c r="R114" t="n">
-        <v>7328332</v>
+        <v>7328300</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13185,7 +13167,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13195,7 +13177,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13226,48 +13208,60 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135358926</v>
+        <v>135357260</v>
       </c>
       <c r="B115" t="n">
-        <v>100806</v>
+        <v>99195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222584</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>657781</v>
+        <v>657949</v>
       </c>
       <c r="R115" t="n">
-        <v>7328326</v>
+        <v>7328433</v>
       </c>
       <c r="S115" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13296,7 +13290,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13306,7 +13300,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13315,18 +13314,19 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13337,32 +13337,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135358920</v>
+        <v>135358537</v>
       </c>
       <c r="B116" t="n">
-        <v>79963</v>
+        <v>106309</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>221725</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>657852</v>
+        <v>657761</v>
       </c>
       <c r="R116" t="n">
-        <v>7328299</v>
+        <v>7328385</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13432,12 +13432,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13448,10 +13448,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135358863</v>
+        <v>135358540</v>
       </c>
       <c r="B117" t="n">
-        <v>95840</v>
+        <v>98066</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13459,21 +13459,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1004672</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13483,13 +13483,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>658147</v>
+        <v>657728</v>
       </c>
       <c r="R117" t="n">
-        <v>7328286</v>
+        <v>7328365</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13543,12 +13543,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13559,32 +13559,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135358229</v>
+        <v>135357257</v>
       </c>
       <c r="B118" t="n">
-        <v>79373</v>
+        <v>99217</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13594,10 +13594,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>658194</v>
+        <v>657988</v>
       </c>
       <c r="R118" t="n">
-        <v>7328255</v>
+        <v>7328384</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13627,9 +13627,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13644,12 +13654,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13660,32 +13670,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135358230</v>
+        <v>135358927</v>
       </c>
       <c r="B119" t="n">
-        <v>79373</v>
+        <v>99217</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13695,13 +13705,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>658217</v>
+        <v>657781</v>
       </c>
       <c r="R119" t="n">
-        <v>7328285</v>
+        <v>7328332</v>
       </c>
       <c r="S119" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13728,9 +13738,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13745,12 +13765,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13761,32 +13781,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135358858</v>
+        <v>135358926</v>
       </c>
       <c r="B120" t="n">
-        <v>79373</v>
+        <v>100806</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>222584</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13796,13 +13816,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>658204</v>
+        <v>657781</v>
       </c>
       <c r="R120" t="n">
-        <v>7328271</v>
+        <v>7328326</v>
       </c>
       <c r="S120" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13831,7 +13851,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13841,7 +13861,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13872,10 +13892,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135358857</v>
+        <v>135358920</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>79963</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13883,21 +13903,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13907,10 +13927,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>658192</v>
+        <v>657852</v>
       </c>
       <c r="R121" t="n">
-        <v>7328281</v>
+        <v>7328299</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13942,7 +13962,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13952,12 +13972,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13981,6 +13996,990 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>135358863</v>
+      </c>
+      <c r="B122" t="n">
+        <v>95840</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>658147</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7328286</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>135358229</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>658194</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7328255</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>135358506</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>658212</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7328246</v>
+      </c>
+      <c r="S124" t="n">
+        <v>6</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135358507</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>658198</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7328199</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135358508</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>658194</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7328167</v>
+      </c>
+      <c r="S126" t="n">
+        <v>8</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135358230</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>658217</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7328285</v>
+      </c>
+      <c r="S127" t="n">
+        <v>14</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135358505</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>658205</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7328283</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>135358858</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>658204</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7328271</v>
+      </c>
+      <c r="S129" t="n">
+        <v>29</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -24815,7 +24815,7 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AY256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -25373,10 +25373,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135358529</v>
+        <v>135435470</v>
       </c>
       <c r="B223" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25384,37 +25384,41 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>657920</v>
+        <v>657931</v>
       </c>
       <c r="R223" t="n">
-        <v>7328326</v>
+        <v>7328314</v>
       </c>
       <c r="S223" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25443,7 +25447,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25453,12 +25457,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>3st</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25473,12 +25472,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -25489,7 +25488,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135362228</v>
+        <v>135358529</v>
       </c>
       <c r="B224" t="n">
         <v>58079</v>
@@ -25518,23 +25517,19 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>657944</v>
+        <v>657920</v>
       </c>
       <c r="R224" t="n">
-        <v>7328343</v>
+        <v>7328326</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25563,7 +25558,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25573,7 +25568,12 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25588,12 +25588,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25604,27 +25604,27 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135358864</v>
+        <v>135362228</v>
       </c>
       <c r="B225" t="n">
-        <v>5201</v>
+        <v>58079</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -25633,19 +25633,23 @@
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>658134</v>
+        <v>657944</v>
       </c>
       <c r="R225" t="n">
-        <v>7328300</v>
+        <v>7328343</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25674,7 +25678,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25684,7 +25688,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25699,12 +25703,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -25715,60 +25719,48 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135357260</v>
+        <v>135358864</v>
       </c>
       <c r="B226" t="n">
-        <v>99195</v>
+        <v>5201</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>657949</v>
+        <v>658134</v>
       </c>
       <c r="R226" t="n">
-        <v>7328433</v>
+        <v>7328300</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25797,7 +25789,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25807,12 +25799,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25821,19 +25808,18 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -25844,48 +25830,60 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135357535</v>
+        <v>135357260</v>
       </c>
       <c r="B227" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>658001</v>
+        <v>657949</v>
       </c>
       <c r="R227" t="n">
-        <v>7328390</v>
+        <v>7328433</v>
       </c>
       <c r="S227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25914,7 +25912,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25924,7 +25922,12 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25933,18 +25936,19 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -25955,7 +25959,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135358537</v>
+        <v>135357535</v>
       </c>
       <c r="B228" t="n">
         <v>106309</v>
@@ -25986,17 +25990,17 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>657761</v>
+        <v>658001</v>
       </c>
       <c r="R228" t="n">
-        <v>7328385</v>
+        <v>7328390</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26025,7 +26029,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26035,7 +26039,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26050,12 +26054,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26066,10 +26070,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135358540</v>
+        <v>135358537</v>
       </c>
       <c r="B229" t="n">
-        <v>98066</v>
+        <v>106309</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26077,21 +26081,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26101,13 +26105,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>657728</v>
+        <v>657761</v>
       </c>
       <c r="R229" t="n">
-        <v>7328365</v>
+        <v>7328385</v>
       </c>
       <c r="S229" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26136,7 +26140,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26146,7 +26150,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26177,10 +26181,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135357257</v>
+        <v>135358540</v>
       </c>
       <c r="B230" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26188,21 +26192,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26212,13 +26216,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>657988</v>
+        <v>657728</v>
       </c>
       <c r="R230" t="n">
-        <v>7328384</v>
+        <v>7328365</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26247,7 +26251,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -26257,7 +26261,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26272,12 +26276,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -26288,7 +26292,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135357530</v>
+        <v>135357257</v>
       </c>
       <c r="B231" t="n">
         <v>99217</v>
@@ -26319,14 +26323,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>657995</v>
+        <v>657988</v>
       </c>
       <c r="R231" t="n">
-        <v>7328356</v>
+        <v>7328384</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -26358,7 +26362,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26368,12 +26372,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Elin G</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26388,12 +26387,12 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -26404,7 +26403,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135358927</v>
+        <v>135357530</v>
       </c>
       <c r="B232" t="n">
         <v>99217</v>
@@ -26435,14 +26434,14 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>657781</v>
+        <v>657995</v>
       </c>
       <c r="R232" t="n">
-        <v>7328332</v>
+        <v>7328356</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -26474,7 +26473,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26484,7 +26483,12 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Elin G</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26499,12 +26503,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -26515,7 +26519,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135362223</v>
+        <v>135358927</v>
       </c>
       <c r="B233" t="n">
         <v>99217</v>
@@ -26550,10 +26554,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>658012</v>
+        <v>657781</v>
       </c>
       <c r="R233" t="n">
-        <v>7328314</v>
+        <v>7328332</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -26585,7 +26589,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26595,7 +26599,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26610,12 +26614,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -26626,7 +26630,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135363849</v>
+        <v>135362223</v>
       </c>
       <c r="B234" t="n">
         <v>99217</v>
@@ -26661,10 +26665,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>657813</v>
+        <v>658012</v>
       </c>
       <c r="R234" t="n">
-        <v>7328352</v>
+        <v>7328314</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -26696,7 +26700,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26706,7 +26710,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26721,12 +26725,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -26737,7 +26741,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135363851</v>
+        <v>135363849</v>
       </c>
       <c r="B235" t="n">
         <v>99217</v>
@@ -26772,10 +26776,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>657575</v>
+        <v>657813</v>
       </c>
       <c r="R235" t="n">
-        <v>7328321</v>
+        <v>7328352</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -26807,7 +26811,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26817,7 +26821,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26837,7 +26841,7 @@
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -26848,10 +26852,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135357533</v>
+        <v>135363851</v>
       </c>
       <c r="B236" t="n">
-        <v>100806</v>
+        <v>99217</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26859,34 +26863,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>222584</v>
+        <v>221952</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>657997</v>
+        <v>657575</v>
       </c>
       <c r="R236" t="n">
-        <v>7328373</v>
+        <v>7328321</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -26918,7 +26922,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26928,7 +26932,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26943,12 +26947,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26959,7 +26963,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135358926</v>
+        <v>135357533</v>
       </c>
       <c r="B237" t="n">
         <v>100806</v>
@@ -26990,17 +26994,17 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>657781</v>
+        <v>657997</v>
       </c>
       <c r="R237" t="n">
-        <v>7328326</v>
+        <v>7328373</v>
       </c>
       <c r="S237" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -27029,7 +27033,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27039,7 +27043,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27054,12 +27058,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27070,32 +27074,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135358920</v>
+        <v>135358926</v>
       </c>
       <c r="B238" t="n">
-        <v>79963</v>
+        <v>100806</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>229821</v>
+        <v>222584</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -27105,13 +27109,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>657852</v>
+        <v>657781</v>
       </c>
       <c r="R238" t="n">
-        <v>7328299</v>
+        <v>7328326</v>
       </c>
       <c r="S238" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27140,7 +27144,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27150,7 +27154,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27181,32 +27185,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135358863</v>
+        <v>135358920</v>
       </c>
       <c r="B239" t="n">
-        <v>95840</v>
+        <v>79963</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1004672</v>
+        <v>229821</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -27216,10 +27220,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>658147</v>
+        <v>657852</v>
       </c>
       <c r="R239" t="n">
-        <v>7328286</v>
+        <v>7328299</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -27251,7 +27255,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27261,7 +27265,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27292,32 +27296,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135357825</v>
+        <v>135358863</v>
       </c>
       <c r="B240" t="n">
-        <v>92245</v>
+        <v>95840</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>658</v>
+        <v>1004672</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -27327,13 +27331,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>658190</v>
+        <v>658147</v>
       </c>
       <c r="R240" t="n">
-        <v>7328207</v>
+        <v>7328286</v>
       </c>
       <c r="S240" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27362,7 +27366,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27372,7 +27376,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27387,22 +27391,26 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY240" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135362199</v>
+        <v>135357825</v>
       </c>
       <c r="B241" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27410,21 +27418,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27434,13 +27442,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>658211</v>
+        <v>658190</v>
       </c>
       <c r="R241" t="n">
-        <v>7328232</v>
+        <v>7328207</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27469,7 +27477,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27479,7 +27487,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27494,26 +27502,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY241" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135357823</v>
+        <v>135362199</v>
       </c>
       <c r="B242" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27521,21 +27525,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27545,13 +27549,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>658198</v>
+        <v>658211</v>
       </c>
       <c r="R242" t="n">
-        <v>7328244</v>
+        <v>7328232</v>
       </c>
       <c r="S242" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27580,7 +27584,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27590,7 +27594,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27605,22 +27609,26 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY242" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135362200</v>
+        <v>135357823</v>
       </c>
       <c r="B243" t="n">
-        <v>83222</v>
+        <v>91970</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27628,21 +27636,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27652,13 +27660,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>658209</v>
+        <v>658198</v>
       </c>
       <c r="R243" t="n">
-        <v>7328233</v>
+        <v>7328244</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27687,7 +27695,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27697,12 +27705,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27717,48 +27720,44 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY243" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135358229</v>
+        <v>135362200</v>
       </c>
       <c r="B244" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27768,10 +27767,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>658194</v>
+        <v>658209</v>
       </c>
       <c r="R244" t="n">
-        <v>7328255</v>
+        <v>7328233</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -27801,9 +27800,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27818,12 +27832,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27834,7 +27848,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135358506</v>
+        <v>135358229</v>
       </c>
       <c r="B245" t="n">
         <v>79373</v>
@@ -27869,13 +27883,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>658212</v>
+        <v>658194</v>
       </c>
       <c r="R245" t="n">
-        <v>7328246</v>
+        <v>7328255</v>
       </c>
       <c r="S245" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27902,19 +27916,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27929,12 +27933,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -27945,7 +27949,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135358507</v>
+        <v>135358506</v>
       </c>
       <c r="B246" t="n">
         <v>79373</v>
@@ -27980,13 +27984,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>658198</v>
+        <v>658212</v>
       </c>
       <c r="R246" t="n">
-        <v>7328199</v>
+        <v>7328246</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28015,7 +28019,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28025,7 +28029,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28056,7 +28060,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135358508</v>
+        <v>135358507</v>
       </c>
       <c r="B247" t="n">
         <v>79373</v>
@@ -28091,13 +28095,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>658194</v>
+        <v>658198</v>
       </c>
       <c r="R247" t="n">
-        <v>7328167</v>
+        <v>7328199</v>
       </c>
       <c r="S247" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28126,7 +28130,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28136,7 +28140,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28167,7 +28171,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135362197</v>
+        <v>135358508</v>
       </c>
       <c r="B248" t="n">
         <v>79373</v>
@@ -28202,13 +28206,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>658207</v>
+        <v>658194</v>
       </c>
       <c r="R248" t="n">
-        <v>7328242</v>
+        <v>7328167</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28237,7 +28241,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28247,7 +28251,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28262,12 +28266,12 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -28278,7 +28282,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135362198</v>
+        <v>135362197</v>
       </c>
       <c r="B249" t="n">
         <v>79373</v>
@@ -28313,10 +28317,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>658209</v>
+        <v>658207</v>
       </c>
       <c r="R249" t="n">
-        <v>7328235</v>
+        <v>7328242</v>
       </c>
       <c r="S249" t="n">
         <v>5</v>
@@ -28348,7 +28352,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28358,7 +28362,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28389,53 +28393,48 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135357824</v>
+        <v>135362198</v>
       </c>
       <c r="B250" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>658192</v>
+        <v>658209</v>
       </c>
       <c r="R250" t="n">
-        <v>7328225</v>
+        <v>7328235</v>
       </c>
       <c r="S250" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28464,7 +28463,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28474,12 +28473,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28494,60 +28488,69 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY250" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135358230</v>
+        <v>135357824</v>
       </c>
       <c r="B251" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>658217</v>
+        <v>658192</v>
       </c>
       <c r="R251" t="n">
-        <v>7328285</v>
+        <v>7328225</v>
       </c>
       <c r="S251" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28574,9 +28577,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28591,23 +28609,19 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY251" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135358505</v>
+        <v>135358230</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28642,13 +28656,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>658205</v>
+        <v>658217</v>
       </c>
       <c r="R252" t="n">
-        <v>7328283</v>
+        <v>7328285</v>
       </c>
       <c r="S252" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28675,19 +28689,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28702,12 +28706,12 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -28718,7 +28722,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135358858</v>
+        <v>135358505</v>
       </c>
       <c r="B253" t="n">
         <v>79373</v>
@@ -28753,13 +28757,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>658204</v>
+        <v>658205</v>
       </c>
       <c r="R253" t="n">
-        <v>7328271</v>
+        <v>7328283</v>
       </c>
       <c r="S253" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28788,7 +28792,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28798,7 +28802,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28813,12 +28817,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28829,7 +28833,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135362196</v>
+        <v>135358858</v>
       </c>
       <c r="B254" t="n">
         <v>79373</v>
@@ -28867,10 +28871,10 @@
         <v>658204</v>
       </c>
       <c r="R254" t="n">
-        <v>7328276</v>
+        <v>7328271</v>
       </c>
       <c r="S254" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28899,7 +28903,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28909,7 +28913,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28924,12 +28928,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -28940,32 +28944,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135358857</v>
+        <v>135362196</v>
       </c>
       <c r="B255" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28975,10 +28979,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>658192</v>
+        <v>658204</v>
       </c>
       <c r="R255" t="n">
-        <v>7328281</v>
+        <v>7328276</v>
       </c>
       <c r="S255" t="n">
         <v>5</v>
@@ -29010,7 +29014,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29020,12 +29024,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29040,15 +29039,131 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B256" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S256" t="n">
+        <v>5</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX255" t="inlineStr">
+      <c r="AX256" t="inlineStr">
         <is>
           <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
-      <c r="AY255" t="inlineStr">
+      <c r="AY256" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY256"/>
+  <dimension ref="A1:AY259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14304,10 +14304,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135356945</v>
+        <v>135435690</v>
       </c>
       <c r="B124" t="n">
-        <v>91937</v>
+        <v>96678</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14315,21 +14315,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>2166</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657999</v>
+        <v>658005</v>
       </c>
       <c r="R124" t="n">
-        <v>7328359</v>
+        <v>7328407</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14369,22 +14369,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>00:42</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>00:42</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14399,12 +14399,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson, Jorma Salmgren, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -14415,10 +14415,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135356947</v>
+        <v>135435692</v>
       </c>
       <c r="B125" t="n">
-        <v>91937</v>
+        <v>96678</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14426,21 +14426,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>2166</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14450,13 +14450,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657973</v>
+        <v>657959</v>
       </c>
       <c r="R125" t="n">
-        <v>7328369</v>
+        <v>7328390</v>
       </c>
       <c r="S125" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14480,22 +14480,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14510,12 +14510,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson, Jorma Salmgren, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14526,32 +14526,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356936</v>
+        <v>135356945</v>
       </c>
       <c r="B126" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14561,13 +14561,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>658123</v>
+        <v>657999</v>
       </c>
       <c r="R126" t="n">
-        <v>7328269</v>
+        <v>7328359</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14637,32 +14637,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356938</v>
+        <v>135356947</v>
       </c>
       <c r="B127" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14672,13 +14672,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>658123</v>
+        <v>657973</v>
       </c>
       <c r="R127" t="n">
-        <v>7328290</v>
+        <v>7328369</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14748,7 +14748,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356939</v>
+        <v>135356936</v>
       </c>
       <c r="B128" t="n">
         <v>79373</v>
@@ -14783,10 +14783,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>658104</v>
+        <v>658123</v>
       </c>
       <c r="R128" t="n">
-        <v>7328291</v>
+        <v>7328269</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14859,7 +14859,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356940</v>
+        <v>135356938</v>
       </c>
       <c r="B129" t="n">
         <v>79373</v>
@@ -14894,10 +14894,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>658075</v>
+        <v>658123</v>
       </c>
       <c r="R129" t="n">
-        <v>7328297</v>
+        <v>7328290</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14970,7 +14970,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135356941</v>
+        <v>135356939</v>
       </c>
       <c r="B130" t="n">
         <v>79373</v>
@@ -15005,13 +15005,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>658052</v>
+        <v>658104</v>
       </c>
       <c r="R130" t="n">
-        <v>7328288</v>
+        <v>7328291</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15081,7 +15081,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135356946</v>
+        <v>135356940</v>
       </c>
       <c r="B131" t="n">
         <v>79373</v>
@@ -15116,13 +15116,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657993</v>
+        <v>658075</v>
       </c>
       <c r="R131" t="n">
-        <v>7328349</v>
+        <v>7328297</v>
       </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15192,7 +15192,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135356948</v>
+        <v>135356941</v>
       </c>
       <c r="B132" t="n">
         <v>79373</v>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>658007</v>
+        <v>658052</v>
       </c>
       <c r="R132" t="n">
-        <v>7328388</v>
+        <v>7328288</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15303,7 +15303,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135356951</v>
+        <v>135356946</v>
       </c>
       <c r="B133" t="n">
         <v>79373</v>
@@ -15338,13 +15338,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>658045</v>
+        <v>657993</v>
       </c>
       <c r="R133" t="n">
-        <v>7328393</v>
+        <v>7328349</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15414,7 +15414,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135356952</v>
+        <v>135356948</v>
       </c>
       <c r="B134" t="n">
         <v>79373</v>
@@ -15449,13 +15449,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>658067</v>
+        <v>658007</v>
       </c>
       <c r="R134" t="n">
-        <v>7328396</v>
+        <v>7328388</v>
       </c>
       <c r="S134" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15525,7 +15525,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135357250</v>
+        <v>135356951</v>
       </c>
       <c r="B135" t="n">
         <v>79373</v>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>658064</v>
+        <v>658045</v>
       </c>
       <c r="R135" t="n">
-        <v>7328265</v>
+        <v>7328393</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15620,12 +15620,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -15636,7 +15636,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135357251</v>
+        <v>135356952</v>
       </c>
       <c r="B136" t="n">
         <v>79373</v>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>658041</v>
+        <v>658067</v>
       </c>
       <c r="R136" t="n">
-        <v>7328283</v>
+        <v>7328396</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15731,12 +15731,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -15747,7 +15747,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135357253</v>
+        <v>135357250</v>
       </c>
       <c r="B137" t="n">
         <v>79373</v>
@@ -15782,10 +15782,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>657993</v>
+        <v>658064</v>
       </c>
       <c r="R137" t="n">
-        <v>7328350</v>
+        <v>7328265</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15858,7 +15858,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135357259</v>
+        <v>135357251</v>
       </c>
       <c r="B138" t="n">
         <v>79373</v>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>657958</v>
+        <v>658041</v>
       </c>
       <c r="R138" t="n">
-        <v>7328432</v>
+        <v>7328283</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15969,7 +15969,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135357262</v>
+        <v>135357253</v>
       </c>
       <c r="B139" t="n">
         <v>79373</v>
@@ -16004,10 +16004,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>657758</v>
+        <v>657993</v>
       </c>
       <c r="R139" t="n">
-        <v>7328354</v>
+        <v>7328350</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16080,7 +16080,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135357528</v>
+        <v>135357259</v>
       </c>
       <c r="B140" t="n">
         <v>79373</v>
@@ -16111,14 +16111,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>658017</v>
+        <v>657958</v>
       </c>
       <c r="R140" t="n">
-        <v>7328347</v>
+        <v>7328432</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16175,12 +16175,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16191,7 +16191,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357537</v>
+        <v>135357262</v>
       </c>
       <c r="B141" t="n">
         <v>79373</v>
@@ -16222,14 +16222,14 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>657993</v>
+        <v>657758</v>
       </c>
       <c r="R141" t="n">
-        <v>7328386</v>
+        <v>7328354</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16286,12 +16286,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -16302,7 +16302,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357546</v>
+        <v>135357528</v>
       </c>
       <c r="B142" t="n">
         <v>79373</v>
@@ -16337,13 +16337,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>658088</v>
+        <v>658017</v>
       </c>
       <c r="R142" t="n">
-        <v>7328408</v>
+        <v>7328347</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16413,7 +16413,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357547</v>
+        <v>135357537</v>
       </c>
       <c r="B143" t="n">
         <v>79373</v>
@@ -16448,10 +16448,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>658088</v>
+        <v>657993</v>
       </c>
       <c r="R143" t="n">
-        <v>7328417</v>
+        <v>7328386</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16524,7 +16524,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135357833</v>
+        <v>135357546</v>
       </c>
       <c r="B144" t="n">
         <v>79373</v>
@@ -16555,17 +16555,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>658099</v>
+        <v>658088</v>
       </c>
       <c r="R144" t="n">
-        <v>7328272</v>
+        <v>7328408</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16619,19 +16619,23 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135357834</v>
+        <v>135357547</v>
       </c>
       <c r="B145" t="n">
         <v>79373</v>
@@ -16662,17 +16666,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
         <v>658088</v>
       </c>
       <c r="R145" t="n">
-        <v>7328303</v>
+        <v>7328417</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16701,7 +16705,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16711,12 +16715,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Apothesier</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16731,19 +16730,23 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135357836</v>
+        <v>135357833</v>
       </c>
       <c r="B146" t="n">
         <v>79373</v>
@@ -16778,13 +16781,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>658080</v>
+        <v>658099</v>
       </c>
       <c r="R146" t="n">
-        <v>7328309</v>
+        <v>7328272</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16813,7 +16816,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16823,7 +16826,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16850,7 +16853,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357839</v>
+        <v>135357834</v>
       </c>
       <c r="B147" t="n">
         <v>79373</v>
@@ -16885,10 +16888,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>658054</v>
+        <v>658088</v>
       </c>
       <c r="R147" t="n">
-        <v>7328327</v>
+        <v>7328303</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -16920,7 +16923,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16930,12 +16933,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Apothesier</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16962,7 +16965,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135358515</v>
+        <v>135357836</v>
       </c>
       <c r="B148" t="n">
         <v>79373</v>
@@ -16997,13 +17000,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>658143</v>
+        <v>658080</v>
       </c>
       <c r="R148" t="n">
-        <v>7328264</v>
+        <v>7328309</v>
       </c>
       <c r="S148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17032,7 +17035,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17042,7 +17045,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17057,23 +17060,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135358519</v>
+        <v>135357839</v>
       </c>
       <c r="B149" t="n">
         <v>79373</v>
@@ -17108,13 +17107,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>658102</v>
+        <v>658054</v>
       </c>
       <c r="R149" t="n">
-        <v>7328301</v>
+        <v>7328327</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17143,7 +17142,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17153,7 +17152,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17168,23 +17172,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135358521</v>
+        <v>135358515</v>
       </c>
       <c r="B150" t="n">
         <v>79373</v>
@@ -17219,13 +17219,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>658050</v>
+        <v>658143</v>
       </c>
       <c r="R150" t="n">
-        <v>7328312</v>
+        <v>7328264</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17264,12 +17264,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>mycket</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17300,7 +17295,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135358525</v>
+        <v>135358519</v>
       </c>
       <c r="B151" t="n">
         <v>79373</v>
@@ -17335,10 +17330,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>657982</v>
+        <v>658102</v>
       </c>
       <c r="R151" t="n">
-        <v>7328312</v>
+        <v>7328301</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17370,7 +17365,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17380,7 +17375,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17411,7 +17406,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135358532</v>
+        <v>135358521</v>
       </c>
       <c r="B152" t="n">
         <v>79373</v>
@@ -17446,13 +17441,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>657854</v>
+        <v>658050</v>
       </c>
       <c r="R152" t="n">
-        <v>7328329</v>
+        <v>7328312</v>
       </c>
       <c r="S152" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17481,7 +17476,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17491,7 +17486,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17522,7 +17522,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135358533</v>
+        <v>135358525</v>
       </c>
       <c r="B153" t="n">
         <v>79373</v>
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>657843</v>
+        <v>657982</v>
       </c>
       <c r="R153" t="n">
-        <v>7328352</v>
+        <v>7328312</v>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17633,7 +17633,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135358536</v>
+        <v>135358532</v>
       </c>
       <c r="B154" t="n">
         <v>79373</v>
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>657778</v>
+        <v>657854</v>
       </c>
       <c r="R154" t="n">
-        <v>7328385</v>
+        <v>7328329</v>
       </c>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17744,7 +17744,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135358538</v>
+        <v>135358533</v>
       </c>
       <c r="B155" t="n">
         <v>79373</v>
@@ -17779,13 +17779,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>657756</v>
+        <v>657843</v>
       </c>
       <c r="R155" t="n">
-        <v>7328370</v>
+        <v>7328352</v>
       </c>
       <c r="S155" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17855,7 +17855,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135358861</v>
+        <v>135358536</v>
       </c>
       <c r="B156" t="n">
         <v>79373</v>
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>658151</v>
+        <v>657778</v>
       </c>
       <c r="R156" t="n">
-        <v>7328266</v>
+        <v>7328385</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17950,12 +17950,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -17966,7 +17966,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135358866</v>
+        <v>135358538</v>
       </c>
       <c r="B157" t="n">
         <v>79373</v>
@@ -18001,13 +18001,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>658124</v>
+        <v>657756</v>
       </c>
       <c r="R157" t="n">
-        <v>7328278</v>
+        <v>7328370</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18061,12 +18061,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -18077,7 +18077,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135358871</v>
+        <v>135358861</v>
       </c>
       <c r="B158" t="n">
         <v>79373</v>
@@ -18112,10 +18112,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>658080</v>
+        <v>658151</v>
       </c>
       <c r="R158" t="n">
-        <v>7328268</v>
+        <v>7328266</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18188,7 +18188,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135358904</v>
+        <v>135358866</v>
       </c>
       <c r="B159" t="n">
         <v>79373</v>
@@ -18223,10 +18223,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>658009</v>
+        <v>658124</v>
       </c>
       <c r="R159" t="n">
-        <v>7328280</v>
+        <v>7328278</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18299,7 +18299,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358909</v>
+        <v>135358871</v>
       </c>
       <c r="B160" t="n">
         <v>79373</v>
@@ -18334,10 +18334,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>657975</v>
+        <v>658080</v>
       </c>
       <c r="R160" t="n">
-        <v>7328291</v>
+        <v>7328268</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18410,7 +18410,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358912</v>
+        <v>135358904</v>
       </c>
       <c r="B161" t="n">
         <v>79373</v>
@@ -18445,13 +18445,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>657974</v>
+        <v>658009</v>
       </c>
       <c r="R161" t="n">
-        <v>7328302</v>
+        <v>7328280</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18521,7 +18521,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358914</v>
+        <v>135358909</v>
       </c>
       <c r="B162" t="n">
         <v>79373</v>
@@ -18556,10 +18556,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>657914</v>
+        <v>657975</v>
       </c>
       <c r="R162" t="n">
-        <v>7328308</v>
+        <v>7328291</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18632,7 +18632,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135358918</v>
+        <v>135358912</v>
       </c>
       <c r="B163" t="n">
         <v>79373</v>
@@ -18667,13 +18667,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>657896</v>
+        <v>657974</v>
       </c>
       <c r="R163" t="n">
-        <v>7328293</v>
+        <v>7328302</v>
       </c>
       <c r="S163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18743,7 +18743,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135358924</v>
+        <v>135358914</v>
       </c>
       <c r="B164" t="n">
         <v>79373</v>
@@ -18778,10 +18778,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>657769</v>
+        <v>657914</v>
       </c>
       <c r="R164" t="n">
-        <v>7328319</v>
+        <v>7328308</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18813,7 +18813,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18854,7 +18854,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135362213</v>
+        <v>135358918</v>
       </c>
       <c r="B165" t="n">
         <v>79373</v>
@@ -18889,10 +18889,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>658104</v>
+        <v>657896</v>
       </c>
       <c r="R165" t="n">
-        <v>7328299</v>
+        <v>7328293</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18949,12 +18949,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -18965,7 +18965,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135362215</v>
+        <v>135358924</v>
       </c>
       <c r="B166" t="n">
         <v>79373</v>
@@ -19000,10 +19000,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>658087</v>
+        <v>657769</v>
       </c>
       <c r="R166" t="n">
-        <v>7328304</v>
+        <v>7328319</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19060,12 +19060,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -19076,7 +19076,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135362218</v>
+        <v>135362213</v>
       </c>
       <c r="B167" t="n">
         <v>79373</v>
@@ -19111,10 +19111,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>658087</v>
+        <v>658104</v>
       </c>
       <c r="R167" t="n">
-        <v>7328321</v>
+        <v>7328299</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19187,7 +19187,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135362219</v>
+        <v>135362215</v>
       </c>
       <c r="B168" t="n">
         <v>79373</v>
@@ -19222,10 +19222,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>658063</v>
+        <v>658087</v>
       </c>
       <c r="R168" t="n">
-        <v>7328322</v>
+        <v>7328304</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19298,7 +19298,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135362220</v>
+        <v>135362218</v>
       </c>
       <c r="B169" t="n">
         <v>79373</v>
@@ -19333,10 +19333,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>658030</v>
+        <v>658087</v>
       </c>
       <c r="R169" t="n">
-        <v>7328315</v>
+        <v>7328321</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19409,7 +19409,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>135362221</v>
+        <v>135362219</v>
       </c>
       <c r="B170" t="n">
         <v>79373</v>
@@ -19444,10 +19444,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>658014</v>
+        <v>658063</v>
       </c>
       <c r="R170" t="n">
-        <v>7328319</v>
+        <v>7328322</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19520,7 +19520,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>135362224</v>
+        <v>135362220</v>
       </c>
       <c r="B171" t="n">
         <v>79373</v>
@@ -19555,10 +19555,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>657988</v>
+        <v>658030</v>
       </c>
       <c r="R171" t="n">
-        <v>7328334</v>
+        <v>7328315</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19631,7 +19631,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>135362225</v>
+        <v>135362221</v>
       </c>
       <c r="B172" t="n">
         <v>79373</v>
@@ -19666,10 +19666,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>657993</v>
+        <v>658014</v>
       </c>
       <c r="R172" t="n">
-        <v>7328337</v>
+        <v>7328319</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19742,7 +19742,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>135362226</v>
+        <v>135362224</v>
       </c>
       <c r="B173" t="n">
         <v>79373</v>
@@ -19777,10 +19777,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>657964</v>
+        <v>657988</v>
       </c>
       <c r="R173" t="n">
-        <v>7328341</v>
+        <v>7328334</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19853,7 +19853,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>135362227</v>
+        <v>135362225</v>
       </c>
       <c r="B174" t="n">
         <v>79373</v>
@@ -19888,10 +19888,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>657944</v>
+        <v>657993</v>
       </c>
       <c r="R174" t="n">
-        <v>7328343</v>
+        <v>7328337</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19964,7 +19964,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>135362230</v>
+        <v>135362226</v>
       </c>
       <c r="B175" t="n">
         <v>79373</v>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>657917</v>
+        <v>657964</v>
       </c>
       <c r="R175" t="n">
-        <v>7328337</v>
+        <v>7328341</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20075,7 +20075,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135362231</v>
+        <v>135362227</v>
       </c>
       <c r="B176" t="n">
         <v>79373</v>
@@ -20110,10 +20110,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>657904</v>
+        <v>657944</v>
       </c>
       <c r="R176" t="n">
-        <v>7328322</v>
+        <v>7328343</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20186,7 +20186,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>135362232</v>
+        <v>135362230</v>
       </c>
       <c r="B177" t="n">
         <v>79373</v>
@@ -20221,10 +20221,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>657888</v>
+        <v>657917</v>
       </c>
       <c r="R177" t="n">
-        <v>7328336</v>
+        <v>7328337</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20297,7 +20297,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>135362233</v>
+        <v>135362231</v>
       </c>
       <c r="B178" t="n">
         <v>79373</v>
@@ -20332,10 +20332,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>657877</v>
+        <v>657904</v>
       </c>
       <c r="R178" t="n">
-        <v>7328365</v>
+        <v>7328322</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20408,7 +20408,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135362235</v>
+        <v>135362232</v>
       </c>
       <c r="B179" t="n">
         <v>79373</v>
@@ -20443,13 +20443,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>657845</v>
+        <v>657888</v>
       </c>
       <c r="R179" t="n">
-        <v>7328351</v>
+        <v>7328336</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20519,7 +20519,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>135362236</v>
+        <v>135362233</v>
       </c>
       <c r="B180" t="n">
         <v>79373</v>
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>657838</v>
+        <v>657877</v>
       </c>
       <c r="R180" t="n">
-        <v>7328357</v>
+        <v>7328365</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20630,7 +20630,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>135362237</v>
+        <v>135362235</v>
       </c>
       <c r="B181" t="n">
         <v>79373</v>
@@ -20665,13 +20665,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>657828</v>
+        <v>657845</v>
       </c>
       <c r="R181" t="n">
-        <v>7328359</v>
+        <v>7328351</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20741,7 +20741,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>135362238</v>
+        <v>135362236</v>
       </c>
       <c r="B182" t="n">
         <v>79373</v>
@@ -20776,10 +20776,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>657809</v>
+        <v>657838</v>
       </c>
       <c r="R182" t="n">
-        <v>7328375</v>
+        <v>7328357</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20852,7 +20852,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>135362239</v>
+        <v>135362237</v>
       </c>
       <c r="B183" t="n">
         <v>79373</v>
@@ -20887,13 +20887,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>657794</v>
+        <v>657828</v>
       </c>
       <c r="R183" t="n">
-        <v>7328374</v>
+        <v>7328359</v>
       </c>
       <c r="S183" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20963,7 +20963,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>135362240</v>
+        <v>135362238</v>
       </c>
       <c r="B184" t="n">
         <v>79373</v>
@@ -20998,10 +20998,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>657783</v>
+        <v>657809</v>
       </c>
       <c r="R184" t="n">
-        <v>7328390</v>
+        <v>7328375</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21074,7 +21074,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>135362241</v>
+        <v>135362239</v>
       </c>
       <c r="B185" t="n">
         <v>79373</v>
@@ -21109,13 +21109,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>657750</v>
+        <v>657794</v>
       </c>
       <c r="R185" t="n">
-        <v>7328385</v>
+        <v>7328374</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21185,7 +21185,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135362244</v>
+        <v>135362240</v>
       </c>
       <c r="B186" t="n">
         <v>79373</v>
@@ -21220,13 +21220,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>657725</v>
+        <v>657783</v>
       </c>
       <c r="R186" t="n">
-        <v>7328360</v>
+        <v>7328390</v>
       </c>
       <c r="S186" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21296,7 +21296,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135362245</v>
+        <v>135362241</v>
       </c>
       <c r="B187" t="n">
         <v>79373</v>
@@ -21331,13 +21331,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>657719</v>
+        <v>657750</v>
       </c>
       <c r="R187" t="n">
-        <v>7328375</v>
+        <v>7328385</v>
       </c>
       <c r="S187" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21407,7 +21407,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135362246</v>
+        <v>135362244</v>
       </c>
       <c r="B188" t="n">
         <v>79373</v>
@@ -21442,13 +21442,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>657704</v>
+        <v>657725</v>
       </c>
       <c r="R188" t="n">
-        <v>7328370</v>
+        <v>7328360</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21518,7 +21518,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135362247</v>
+        <v>135362245</v>
       </c>
       <c r="B189" t="n">
         <v>79373</v>
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>657672</v>
+        <v>657719</v>
       </c>
       <c r="R189" t="n">
-        <v>7328366</v>
+        <v>7328375</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21629,7 +21629,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135363846</v>
+        <v>135362246</v>
       </c>
       <c r="B190" t="n">
         <v>79373</v>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>657967</v>
+        <v>657704</v>
       </c>
       <c r="R190" t="n">
-        <v>7328296</v>
+        <v>7328370</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21724,12 +21724,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -21740,7 +21740,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135369266</v>
+        <v>135362247</v>
       </c>
       <c r="B191" t="n">
         <v>79373</v>
@@ -21775,13 +21775,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>657956</v>
+        <v>657672</v>
       </c>
       <c r="R191" t="n">
-        <v>7328278</v>
+        <v>7328366</v>
       </c>
       <c r="S191" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21820,12 +21820,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På större gran.</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21840,19 +21835,23 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY191" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135369277</v>
+        <v>135363846</v>
       </c>
       <c r="B192" t="n">
         <v>79373</v>
@@ -21887,13 +21886,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>657823</v>
+        <v>657967</v>
       </c>
       <c r="R192" t="n">
-        <v>7328337</v>
+        <v>7328296</v>
       </c>
       <c r="S192" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21922,7 +21921,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21932,12 +21931,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>På stor gammal gran.</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21952,19 +21946,23 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135369278</v>
+        <v>135369266</v>
       </c>
       <c r="B193" t="n">
         <v>79373</v>
@@ -21999,13 +21997,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>657778</v>
+        <v>657956</v>
       </c>
       <c r="R193" t="n">
-        <v>7328371</v>
+        <v>7328278</v>
       </c>
       <c r="S193" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22034,7 +22032,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22044,12 +22042,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>På stor gran.</t>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22076,32 +22074,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135358910</v>
+        <v>135369277</v>
       </c>
       <c r="B194" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22111,13 +22109,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>657974</v>
+        <v>657823</v>
       </c>
       <c r="R194" t="n">
-        <v>7328303</v>
+        <v>7328337</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22146,7 +22144,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22156,7 +22154,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På stor gammal gran.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22171,48 +22174,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY194" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135356935</v>
+        <v>135369278</v>
       </c>
       <c r="B195" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22222,13 +22221,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>658122</v>
+        <v>657778</v>
       </c>
       <c r="R195" t="n">
-        <v>7328267</v>
+        <v>7328371</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22257,7 +22256,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22267,7 +22266,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På stor gran.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22282,26 +22286,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY195" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135356950</v>
+        <v>135358910</v>
       </c>
       <c r="B196" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22309,21 +22309,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22333,13 +22333,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>658045</v>
+        <v>657974</v>
       </c>
       <c r="R196" t="n">
-        <v>7328393</v>
+        <v>7328303</v>
       </c>
       <c r="S196" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22393,12 +22393,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -22409,7 +22409,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135357523</v>
+        <v>135356935</v>
       </c>
       <c r="B197" t="n">
         <v>83358</v>
@@ -22440,17 +22440,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>658138</v>
+        <v>658122</v>
       </c>
       <c r="R197" t="n">
-        <v>7328266</v>
+        <v>7328267</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22490,11 +22490,6 @@
       <c r="AB197" t="inlineStr">
         <is>
           <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22509,12 +22504,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -22525,7 +22520,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135358862</v>
+        <v>135356950</v>
       </c>
       <c r="B198" t="n">
         <v>83358</v>
@@ -22560,13 +22555,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>658142</v>
+        <v>658045</v>
       </c>
       <c r="R198" t="n">
-        <v>7328263</v>
+        <v>7328393</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22595,7 +22590,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22605,7 +22600,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22620,12 +22615,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -22636,45 +22631,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135358896</v>
+        <v>135357523</v>
       </c>
       <c r="B199" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>658008</v>
+        <v>658138</v>
       </c>
       <c r="R199" t="n">
-        <v>7328268</v>
+        <v>7328266</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22706,7 +22701,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22716,7 +22711,12 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22731,12 +22731,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -22747,32 +22747,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135358898</v>
+        <v>135358862</v>
       </c>
       <c r="B200" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22782,13 +22782,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>658006</v>
+        <v>658142</v>
       </c>
       <c r="R200" t="n">
-        <v>7328269</v>
+        <v>7328263</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22858,7 +22858,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135363843</v>
+        <v>135358896</v>
       </c>
       <c r="B201" t="n">
         <v>80493</v>
@@ -22893,13 +22893,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>658021</v>
+        <v>658008</v>
       </c>
       <c r="R201" t="n">
-        <v>7328275</v>
+        <v>7328268</v>
       </c>
       <c r="S201" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22949,31 +22949,16 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -22984,7 +22969,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135363845</v>
+        <v>135358898</v>
       </c>
       <c r="B202" t="n">
         <v>80493</v>
@@ -23019,13 +23004,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>658009</v>
+        <v>658006</v>
       </c>
       <c r="R202" t="n">
-        <v>7328284</v>
+        <v>7328269</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -23054,7 +23039,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23064,7 +23049,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23075,31 +23060,16 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -23110,7 +23080,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135369268</v>
+        <v>135363843</v>
       </c>
       <c r="B203" t="n">
         <v>80493</v>
@@ -23145,13 +23115,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>657938</v>
+        <v>658021</v>
       </c>
       <c r="R203" t="n">
-        <v>7328289</v>
+        <v>7328275</v>
       </c>
       <c r="S203" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -23180,7 +23150,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23190,12 +23160,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23206,23 +23171,42 @@
       </c>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY203" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135369280</v>
+        <v>135363845</v>
       </c>
       <c r="B204" t="n">
         <v>80493</v>
@@ -23257,13 +23241,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>657682</v>
+        <v>658009</v>
       </c>
       <c r="R204" t="n">
-        <v>7328376</v>
+        <v>7328284</v>
       </c>
       <c r="S204" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23292,7 +23276,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23302,12 +23286,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23318,26 +23297,45 @@
       </c>
       <c r="AG204" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135358520</v>
+        <v>135369268</v>
       </c>
       <c r="B205" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23345,21 +23343,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23369,13 +23367,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>658099</v>
+        <v>657938</v>
       </c>
       <c r="R205" t="n">
         <v>7328289</v>
       </c>
       <c r="S205" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23404,7 +23402,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23414,7 +23412,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23429,26 +23432,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135358894</v>
+        <v>135369280</v>
       </c>
       <c r="B206" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,21 +23455,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23480,13 +23479,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>658009</v>
+        <v>657682</v>
       </c>
       <c r="R206" t="n">
-        <v>7328269</v>
+        <v>7328376</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23515,7 +23514,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23525,7 +23524,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23540,23 +23544,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY206" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135369269</v>
+        <v>135358520</v>
       </c>
       <c r="B207" t="n">
         <v>80499</v>
@@ -23591,13 +23591,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>657938</v>
+        <v>658099</v>
       </c>
       <c r="R207" t="n">
         <v>7328289</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23636,12 +23636,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23656,22 +23651,26 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>135358516</v>
+        <v>135358894</v>
       </c>
       <c r="B208" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23679,21 +23678,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23703,10 +23702,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>658109</v>
+        <v>658009</v>
       </c>
       <c r="R208" t="n">
-        <v>7328286</v>
+        <v>7328269</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23738,7 +23737,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23748,12 +23747,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>på låga</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23768,12 +23762,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -23784,10 +23778,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135358868</v>
+        <v>135369269</v>
       </c>
       <c r="B209" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23795,21 +23789,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23819,10 +23813,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>658107</v>
+        <v>657938</v>
       </c>
       <c r="R209" t="n">
-        <v>7328286</v>
+        <v>7328289</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23854,7 +23848,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23864,7 +23858,12 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23879,23 +23878,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY209" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135358892</v>
+        <v>135358516</v>
       </c>
       <c r="B210" t="n">
         <v>80500</v>
@@ -23930,13 +23925,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>658011</v>
+        <v>658109</v>
       </c>
       <c r="R210" t="n">
-        <v>7328274</v>
+        <v>7328286</v>
       </c>
       <c r="S210" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23965,7 +23960,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23975,7 +23970,12 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>på låga</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23990,12 +23990,12 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -24006,7 +24006,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135362212</v>
+        <v>135358868</v>
       </c>
       <c r="B211" t="n">
         <v>80500</v>
@@ -24041,10 +24041,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>658112</v>
+        <v>658107</v>
       </c>
       <c r="R211" t="n">
-        <v>7328279</v>
+        <v>7328286</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24101,12 +24101,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -24117,7 +24117,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135363844</v>
+        <v>135358892</v>
       </c>
       <c r="B212" t="n">
         <v>80500</v>
@@ -24152,13 +24152,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>658021</v>
+        <v>658011</v>
       </c>
       <c r="R212" t="n">
-        <v>7328275</v>
+        <v>7328274</v>
       </c>
       <c r="S212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24197,7 +24197,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24208,31 +24208,16 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -24243,53 +24228,48 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135357841</v>
+        <v>135362212</v>
       </c>
       <c r="B213" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>658035</v>
+        <v>658112</v>
       </c>
       <c r="R213" t="n">
-        <v>7328397</v>
+        <v>7328279</v>
       </c>
       <c r="S213" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24318,7 +24298,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24328,12 +24308,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24348,65 +24323,64 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY213" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135357843</v>
+        <v>135363844</v>
       </c>
       <c r="B214" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>658016</v>
+        <v>658021</v>
       </c>
       <c r="R214" t="n">
-        <v>7328389</v>
+        <v>7328275</v>
       </c>
       <c r="S214" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24435,7 +24409,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24445,12 +24419,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24461,23 +24430,42 @@
       </c>
       <c r="AG214" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY214" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135357845</v>
+        <v>135357841</v>
       </c>
       <c r="B215" t="n">
         <v>57975</v>
@@ -24517,10 +24505,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>657975</v>
+        <v>658035</v>
       </c>
       <c r="R215" t="n">
-        <v>7328406</v>
+        <v>7328397</v>
       </c>
       <c r="S215" t="n">
         <v>3</v>
@@ -24552,7 +24540,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24562,7 +24550,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -24594,7 +24582,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135358865</v>
+        <v>135357843</v>
       </c>
       <c r="B216" t="n">
         <v>57975</v>
@@ -24623,19 +24611,24 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>658125</v>
+        <v>658016</v>
       </c>
       <c r="R216" t="n">
-        <v>7328274</v>
+        <v>7328389</v>
       </c>
       <c r="S216" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24664,7 +24657,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -24674,12 +24667,12 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24694,64 +24687,65 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY216" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135369279</v>
+        <v>135357845</v>
       </c>
       <c r="B217" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>657744</v>
+        <v>657975</v>
       </c>
       <c r="R217" t="n">
-        <v>7328367</v>
+        <v>7328406</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24780,7 +24774,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24790,12 +24784,12 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Fågelfjädrar efter tjäder.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24810,44 +24804,44 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135358873</v>
+        <v>135358865</v>
       </c>
       <c r="B218" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24857,10 +24851,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>658080</v>
+        <v>658125</v>
       </c>
       <c r="R218" t="n">
-        <v>7328262</v>
+        <v>7328274</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24892,7 +24886,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24902,7 +24896,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24933,32 +24932,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135357847</v>
+        <v>135369279</v>
       </c>
       <c r="B219" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24968,13 +24967,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>657855</v>
+        <v>657744</v>
       </c>
       <c r="R219" t="n">
-        <v>7328383</v>
+        <v>7328367</v>
       </c>
       <c r="S219" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -25003,7 +25002,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25013,7 +25012,12 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Fågelfjädrar efter tjäder.</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25028,44 +25032,44 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135358530</v>
+        <v>135358873</v>
       </c>
       <c r="B220" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25075,13 +25079,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>657916</v>
+        <v>658080</v>
       </c>
       <c r="R220" t="n">
-        <v>7328337</v>
+        <v>7328262</v>
       </c>
       <c r="S220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -25110,7 +25114,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25120,7 +25124,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25135,12 +25139,12 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -25151,7 +25155,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135358916</v>
+        <v>135357847</v>
       </c>
       <c r="B221" t="n">
         <v>58136</v>
@@ -25186,13 +25190,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>657914</v>
+        <v>657855</v>
       </c>
       <c r="R221" t="n">
-        <v>7328307</v>
+        <v>7328383</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25221,7 +25225,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25231,7 +25235,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25246,23 +25250,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135358921</v>
+        <v>135358530</v>
       </c>
       <c r="B222" t="n">
         <v>58136</v>
@@ -25297,13 +25297,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>657875</v>
+        <v>657916</v>
       </c>
       <c r="R222" t="n">
-        <v>7328357</v>
+        <v>7328337</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25357,12 +25357,12 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -25373,7 +25373,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135435470</v>
+        <v>135358916</v>
       </c>
       <c r="B223" t="n">
         <v>58136</v>
@@ -25401,24 +25401,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>657931</v>
+        <v>657914</v>
       </c>
       <c r="R223" t="n">
-        <v>7328314</v>
+        <v>7328307</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25447,7 +25443,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25457,7 +25453,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25472,12 +25468,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -25488,10 +25484,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135358529</v>
+        <v>135358921</v>
       </c>
       <c r="B224" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25499,21 +25495,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25523,13 +25519,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>657920</v>
+        <v>657875</v>
       </c>
       <c r="R224" t="n">
-        <v>7328326</v>
+        <v>7328357</v>
       </c>
       <c r="S224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25569,11 +25565,6 @@
       <c r="AB224" t="inlineStr">
         <is>
           <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25588,12 +25579,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25604,10 +25595,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135362228</v>
+        <v>135435470</v>
       </c>
       <c r="B225" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25615,41 +25606,41 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>657944</v>
+        <v>657931</v>
       </c>
       <c r="R225" t="n">
-        <v>7328343</v>
+        <v>7328314</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25678,7 +25669,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25688,7 +25679,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25703,12 +25694,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -25719,27 +25710,27 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135358864</v>
+        <v>135358529</v>
       </c>
       <c r="B226" t="n">
-        <v>5201</v>
+        <v>58079</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -25754,13 +25745,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>658134</v>
+        <v>657920</v>
       </c>
       <c r="R226" t="n">
-        <v>7328300</v>
+        <v>7328326</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25789,7 +25780,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25799,7 +25790,12 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25814,12 +25810,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -25830,46 +25826,38 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135357260</v>
+        <v>135362228</v>
       </c>
       <c r="B227" t="n">
-        <v>99195</v>
+        <v>58079</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -25877,10 +25865,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>657949</v>
+        <v>657944</v>
       </c>
       <c r="R227" t="n">
-        <v>7328433</v>
+        <v>7328343</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -25912,7 +25900,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25922,12 +25910,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25936,19 +25919,18 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -25959,10 +25941,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135357535</v>
+        <v>135358864</v>
       </c>
       <c r="B228" t="n">
-        <v>106309</v>
+        <v>5201</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25970,37 +25952,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>221725</v>
+        <v>105930</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>658001</v>
+        <v>658134</v>
       </c>
       <c r="R228" t="n">
-        <v>7328390</v>
+        <v>7328300</v>
       </c>
       <c r="S228" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26029,7 +26011,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26039,7 +26021,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26054,12 +26036,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26070,48 +26052,53 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135358537</v>
+        <v>135435699</v>
       </c>
       <c r="B229" t="n">
-        <v>106309</v>
+        <v>41606</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221725</v>
+        <v>215713</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>657761</v>
+        <v>657973</v>
       </c>
       <c r="R229" t="n">
-        <v>7328385</v>
+        <v>7328356</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26135,22 +26122,27 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>LepiLED Maxi med UV och synligt ljus i VUKU-garderob</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26165,12 +26157,12 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson, Jorma Salmgren, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -26181,48 +26173,60 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135358540</v>
+        <v>135357260</v>
       </c>
       <c r="B230" t="n">
-        <v>98066</v>
+        <v>99195</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>657728</v>
+        <v>657949</v>
       </c>
       <c r="R230" t="n">
-        <v>7328365</v>
+        <v>7328433</v>
       </c>
       <c r="S230" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26251,7 +26255,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -26261,7 +26265,12 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26270,18 +26279,19 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -26292,10 +26302,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135357257</v>
+        <v>135357535</v>
       </c>
       <c r="B231" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26303,37 +26313,37 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>657988</v>
+        <v>658001</v>
       </c>
       <c r="R231" t="n">
-        <v>7328384</v>
+        <v>7328390</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26362,7 +26372,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26372,7 +26382,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26387,12 +26397,12 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -26403,10 +26413,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135357530</v>
+        <v>135358537</v>
       </c>
       <c r="B232" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26414,34 +26424,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>657995</v>
+        <v>657761</v>
       </c>
       <c r="R232" t="n">
-        <v>7328356</v>
+        <v>7328385</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -26473,7 +26483,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26483,12 +26493,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Elin G</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26503,12 +26508,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -26519,10 +26524,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135358927</v>
+        <v>135358540</v>
       </c>
       <c r="B233" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26530,21 +26535,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26554,13 +26559,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>657781</v>
+        <v>657728</v>
       </c>
       <c r="R233" t="n">
-        <v>7328332</v>
+        <v>7328365</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26589,7 +26594,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26599,7 +26604,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26614,12 +26619,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -26630,7 +26635,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135362223</v>
+        <v>135357257</v>
       </c>
       <c r="B234" t="n">
         <v>99217</v>
@@ -26665,10 +26670,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>658012</v>
+        <v>657988</v>
       </c>
       <c r="R234" t="n">
-        <v>7328314</v>
+        <v>7328384</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -26700,7 +26705,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26710,7 +26715,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26725,12 +26730,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -26741,7 +26746,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135363849</v>
+        <v>135357530</v>
       </c>
       <c r="B235" t="n">
         <v>99217</v>
@@ -26772,14 +26777,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>657813</v>
+        <v>657995</v>
       </c>
       <c r="R235" t="n">
-        <v>7328352</v>
+        <v>7328356</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -26811,7 +26816,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26821,7 +26826,12 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Elin G</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26836,12 +26846,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -26852,7 +26862,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135363851</v>
+        <v>135358927</v>
       </c>
       <c r="B236" t="n">
         <v>99217</v>
@@ -26887,10 +26897,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>657575</v>
+        <v>657781</v>
       </c>
       <c r="R236" t="n">
-        <v>7328321</v>
+        <v>7328332</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -26922,7 +26932,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26932,7 +26942,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26947,12 +26957,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26963,10 +26973,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135357533</v>
+        <v>135362223</v>
       </c>
       <c r="B237" t="n">
-        <v>100806</v>
+        <v>99217</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26974,34 +26984,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>222584</v>
+        <v>221952</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>657997</v>
+        <v>658012</v>
       </c>
       <c r="R237" t="n">
-        <v>7328373</v>
+        <v>7328314</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -27033,7 +27043,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27043,7 +27053,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27058,12 +27068,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27074,10 +27084,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135358926</v>
+        <v>135363849</v>
       </c>
       <c r="B238" t="n">
-        <v>100806</v>
+        <v>99217</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27085,21 +27095,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>222584</v>
+        <v>221952</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -27109,13 +27119,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>657781</v>
+        <v>657813</v>
       </c>
       <c r="R238" t="n">
-        <v>7328326</v>
+        <v>7328352</v>
       </c>
       <c r="S238" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27144,7 +27154,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27154,7 +27164,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27169,12 +27179,12 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27185,32 +27195,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135358920</v>
+        <v>135363851</v>
       </c>
       <c r="B239" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -27220,10 +27230,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>657852</v>
+        <v>657575</v>
       </c>
       <c r="R239" t="n">
-        <v>7328299</v>
+        <v>7328321</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -27255,7 +27265,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27265,7 +27275,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27280,12 +27290,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -27296,10 +27306,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135358863</v>
+        <v>135357533</v>
       </c>
       <c r="B240" t="n">
-        <v>95840</v>
+        <v>100806</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27307,34 +27317,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1004672</v>
+        <v>222584</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>658147</v>
+        <v>657997</v>
       </c>
       <c r="R240" t="n">
-        <v>7328286</v>
+        <v>7328373</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -27366,7 +27376,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27376,7 +27386,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27391,12 +27401,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -27407,32 +27417,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135357825</v>
+        <v>135358926</v>
       </c>
       <c r="B241" t="n">
-        <v>92245</v>
+        <v>100806</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>658</v>
+        <v>222584</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27442,13 +27452,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>658190</v>
+        <v>657781</v>
       </c>
       <c r="R241" t="n">
-        <v>7328207</v>
+        <v>7328326</v>
       </c>
       <c r="S241" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27477,7 +27487,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27487,7 +27497,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27502,22 +27512,26 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY241" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135362199</v>
+        <v>135358920</v>
       </c>
       <c r="B242" t="n">
-        <v>79452</v>
+        <v>79963</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27525,21 +27539,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27549,10 +27563,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>658211</v>
+        <v>657852</v>
       </c>
       <c r="R242" t="n">
-        <v>7328232</v>
+        <v>7328299</v>
       </c>
       <c r="S242" t="n">
         <v>5</v>
@@ -27584,7 +27598,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27594,7 +27608,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27609,12 +27623,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27625,32 +27639,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135357823</v>
+        <v>135358863</v>
       </c>
       <c r="B243" t="n">
-        <v>91970</v>
+        <v>95840</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1108</v>
+        <v>1004672</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27660,13 +27674,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>658198</v>
+        <v>658147</v>
       </c>
       <c r="R243" t="n">
-        <v>7328244</v>
+        <v>7328286</v>
       </c>
       <c r="S243" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27695,7 +27709,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27705,7 +27719,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27720,22 +27734,26 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY243" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135362200</v>
+        <v>135357825</v>
       </c>
       <c r="B244" t="n">
-        <v>83222</v>
+        <v>92245</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27743,21 +27761,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27767,13 +27785,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>658209</v>
+        <v>658190</v>
       </c>
       <c r="R244" t="n">
-        <v>7328233</v>
+        <v>7328207</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27802,7 +27820,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27812,12 +27830,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27832,48 +27845,44 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY244" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135358229</v>
+        <v>135362199</v>
       </c>
       <c r="B245" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27883,10 +27892,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>658194</v>
+        <v>658211</v>
       </c>
       <c r="R245" t="n">
-        <v>7328255</v>
+        <v>7328232</v>
       </c>
       <c r="S245" t="n">
         <v>5</v>
@@ -27916,9 +27925,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27933,12 +27952,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -27949,32 +27968,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135358506</v>
+        <v>135357823</v>
       </c>
       <c r="B246" t="n">
-        <v>79373</v>
+        <v>91970</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27984,13 +28003,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>658212</v>
+        <v>658198</v>
       </c>
       <c r="R246" t="n">
-        <v>7328246</v>
+        <v>7328244</v>
       </c>
       <c r="S246" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28019,7 +28038,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28029,7 +28048,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28044,48 +28063,44 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY246" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135358507</v>
+        <v>135362200</v>
       </c>
       <c r="B247" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28095,10 +28110,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>658198</v>
+        <v>658209</v>
       </c>
       <c r="R247" t="n">
-        <v>7328199</v>
+        <v>7328233</v>
       </c>
       <c r="S247" t="n">
         <v>5</v>
@@ -28130,7 +28145,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28140,7 +28155,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28155,12 +28175,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -28171,7 +28191,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135358508</v>
+        <v>135358229</v>
       </c>
       <c r="B248" t="n">
         <v>79373</v>
@@ -28209,10 +28229,10 @@
         <v>658194</v>
       </c>
       <c r="R248" t="n">
-        <v>7328167</v>
+        <v>7328255</v>
       </c>
       <c r="S248" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28239,19 +28259,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28266,12 +28276,12 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -28282,7 +28292,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135362197</v>
+        <v>135358506</v>
       </c>
       <c r="B249" t="n">
         <v>79373</v>
@@ -28317,13 +28327,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>658207</v>
+        <v>658212</v>
       </c>
       <c r="R249" t="n">
-        <v>7328242</v>
+        <v>7328246</v>
       </c>
       <c r="S249" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28352,7 +28362,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28362,7 +28372,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28377,12 +28387,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -28393,7 +28403,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135362198</v>
+        <v>135358507</v>
       </c>
       <c r="B250" t="n">
         <v>79373</v>
@@ -28428,10 +28438,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>658209</v>
+        <v>658198</v>
       </c>
       <c r="R250" t="n">
-        <v>7328235</v>
+        <v>7328199</v>
       </c>
       <c r="S250" t="n">
         <v>5</v>
@@ -28463,7 +28473,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28473,7 +28483,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28488,12 +28498,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -28504,53 +28514,48 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135357824</v>
+        <v>135358508</v>
       </c>
       <c r="B251" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>658192</v>
+        <v>658194</v>
       </c>
       <c r="R251" t="n">
-        <v>7328225</v>
+        <v>7328167</v>
       </c>
       <c r="S251" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28579,7 +28584,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28589,12 +28594,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28609,19 +28609,23 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY251" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135358230</v>
+        <v>135362197</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28656,13 +28660,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>658217</v>
+        <v>658207</v>
       </c>
       <c r="R252" t="n">
-        <v>7328285</v>
+        <v>7328242</v>
       </c>
       <c r="S252" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28689,9 +28693,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28706,12 +28720,12 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -28722,7 +28736,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135358505</v>
+        <v>135362198</v>
       </c>
       <c r="B253" t="n">
         <v>79373</v>
@@ -28757,10 +28771,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>658205</v>
+        <v>658209</v>
       </c>
       <c r="R253" t="n">
-        <v>7328283</v>
+        <v>7328235</v>
       </c>
       <c r="S253" t="n">
         <v>5</v>
@@ -28792,7 +28806,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28802,7 +28816,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28817,12 +28831,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28833,48 +28847,53 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135358858</v>
+        <v>135357824</v>
       </c>
       <c r="B254" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>658204</v>
+        <v>658192</v>
       </c>
       <c r="R254" t="n">
-        <v>7328271</v>
+        <v>7328225</v>
       </c>
       <c r="S254" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28903,7 +28922,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28913,7 +28932,12 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28928,23 +28952,19 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY254" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135362196</v>
+        <v>135358230</v>
       </c>
       <c r="B255" t="n">
         <v>79373</v>
@@ -28979,13 +28999,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>658204</v>
+        <v>658217</v>
       </c>
       <c r="R255" t="n">
-        <v>7328276</v>
+        <v>7328285</v>
       </c>
       <c r="S255" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29012,19 +29032,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29039,12 +29049,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -29055,32 +29065,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135358857</v>
+        <v>135358505</v>
       </c>
       <c r="B256" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -29090,10 +29100,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>658192</v>
+        <v>658205</v>
       </c>
       <c r="R256" t="n">
-        <v>7328281</v>
+        <v>7328283</v>
       </c>
       <c r="S256" t="n">
         <v>5</v>
@@ -29125,7 +29135,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -29135,12 +29145,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29155,15 +29160,353 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>135358858</v>
+      </c>
+      <c r="B257" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>658204</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7328271</v>
+      </c>
+      <c r="S257" t="n">
+        <v>29</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX256" t="inlineStr">
+      <c r="AX257" t="inlineStr">
         <is>
           <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
-      <c r="AY256" t="inlineStr">
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>135362196</v>
+      </c>
+      <c r="B258" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>658204</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7328276</v>
+      </c>
+      <c r="S258" t="n">
+        <v>5</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B259" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S259" t="n">
+        <v>5</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY260"/>
+  <dimension ref="A1:AY261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27746,48 +27746,51 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135358863</v>
+        <v>135521161</v>
       </c>
       <c r="B244" t="n">
-        <v>95840</v>
+        <v>79963</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1004672</v>
+        <v>229821</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>658147</v>
+        <v>657847</v>
       </c>
       <c r="R244" t="n">
-        <v>7328286</v>
+        <v>7328292</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27816,7 +27819,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27826,7 +27829,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27835,54 +27838,71 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY244" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135357825</v>
+        <v>135358863</v>
       </c>
       <c r="B245" t="n">
-        <v>92245</v>
+        <v>95840</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>658</v>
+        <v>1004672</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27892,13 +27912,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>658190</v>
+        <v>658147</v>
       </c>
       <c r="R245" t="n">
-        <v>7328207</v>
+        <v>7328286</v>
       </c>
       <c r="S245" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27927,7 +27947,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27937,7 +27957,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27952,22 +27972,26 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY245" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135362199</v>
+        <v>135357825</v>
       </c>
       <c r="B246" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27975,21 +27999,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27999,13 +28023,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>658211</v>
+        <v>658190</v>
       </c>
       <c r="R246" t="n">
-        <v>7328232</v>
+        <v>7328207</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28034,7 +28058,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28044,7 +28068,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28059,26 +28083,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY246" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135357823</v>
+        <v>135362199</v>
       </c>
       <c r="B247" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28086,21 +28106,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28110,13 +28130,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>658198</v>
+        <v>658211</v>
       </c>
       <c r="R247" t="n">
-        <v>7328244</v>
+        <v>7328232</v>
       </c>
       <c r="S247" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28145,7 +28165,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28155,7 +28175,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28170,22 +28190,26 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY247" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135362200</v>
+        <v>135357823</v>
       </c>
       <c r="B248" t="n">
-        <v>83222</v>
+        <v>91970</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28193,21 +28217,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28217,13 +28241,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>658209</v>
+        <v>658198</v>
       </c>
       <c r="R248" t="n">
-        <v>7328233</v>
+        <v>7328244</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28252,7 +28276,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28262,12 +28286,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28282,48 +28301,44 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY248" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135358229</v>
+        <v>135362200</v>
       </c>
       <c r="B249" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28333,10 +28348,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>658194</v>
+        <v>658209</v>
       </c>
       <c r="R249" t="n">
-        <v>7328255</v>
+        <v>7328233</v>
       </c>
       <c r="S249" t="n">
         <v>5</v>
@@ -28366,9 +28381,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28383,12 +28413,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -28399,7 +28429,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135358506</v>
+        <v>135358229</v>
       </c>
       <c r="B250" t="n">
         <v>79373</v>
@@ -28434,13 +28464,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>658212</v>
+        <v>658194</v>
       </c>
       <c r="R250" t="n">
-        <v>7328246</v>
+        <v>7328255</v>
       </c>
       <c r="S250" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28467,19 +28497,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28494,12 +28514,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -28510,7 +28530,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135358507</v>
+        <v>135358506</v>
       </c>
       <c r="B251" t="n">
         <v>79373</v>
@@ -28545,13 +28565,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>658198</v>
+        <v>658212</v>
       </c>
       <c r="R251" t="n">
-        <v>7328199</v>
+        <v>7328246</v>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28580,7 +28600,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28590,7 +28610,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28621,7 +28641,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135358508</v>
+        <v>135358507</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28656,13 +28676,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>658194</v>
+        <v>658198</v>
       </c>
       <c r="R252" t="n">
-        <v>7328167</v>
+        <v>7328199</v>
       </c>
       <c r="S252" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28691,7 +28711,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28701,7 +28721,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28732,7 +28752,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135362197</v>
+        <v>135358508</v>
       </c>
       <c r="B253" t="n">
         <v>79373</v>
@@ -28767,13 +28787,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>658207</v>
+        <v>658194</v>
       </c>
       <c r="R253" t="n">
-        <v>7328242</v>
+        <v>7328167</v>
       </c>
       <c r="S253" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28802,7 +28822,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28812,7 +28832,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28827,12 +28847,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28843,7 +28863,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135362198</v>
+        <v>135362197</v>
       </c>
       <c r="B254" t="n">
         <v>79373</v>
@@ -28878,10 +28898,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>658209</v>
+        <v>658207</v>
       </c>
       <c r="R254" t="n">
-        <v>7328235</v>
+        <v>7328242</v>
       </c>
       <c r="S254" t="n">
         <v>5</v>
@@ -28913,7 +28933,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28923,7 +28943,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28954,53 +28974,48 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135357824</v>
+        <v>135362198</v>
       </c>
       <c r="B255" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>658192</v>
+        <v>658209</v>
       </c>
       <c r="R255" t="n">
-        <v>7328225</v>
+        <v>7328235</v>
       </c>
       <c r="S255" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29029,7 +29044,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29039,12 +29054,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29059,60 +29069,69 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY255" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135358230</v>
+        <v>135357824</v>
       </c>
       <c r="B256" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>658217</v>
+        <v>658192</v>
       </c>
       <c r="R256" t="n">
-        <v>7328285</v>
+        <v>7328225</v>
       </c>
       <c r="S256" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29139,9 +29158,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29156,23 +29190,19 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY256" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135358505</v>
+        <v>135358230</v>
       </c>
       <c r="B257" t="n">
         <v>79373</v>
@@ -29207,13 +29237,13 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>658205</v>
+        <v>658217</v>
       </c>
       <c r="R257" t="n">
-        <v>7328283</v>
+        <v>7328285</v>
       </c>
       <c r="S257" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29240,19 +29270,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29267,12 +29287,12 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -29283,7 +29303,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135358858</v>
+        <v>135358505</v>
       </c>
       <c r="B258" t="n">
         <v>79373</v>
@@ -29318,13 +29338,13 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>658204</v>
+        <v>658205</v>
       </c>
       <c r="R258" t="n">
-        <v>7328271</v>
+        <v>7328283</v>
       </c>
       <c r="S258" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29353,7 +29373,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -29363,7 +29383,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29378,12 +29398,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -29394,7 +29414,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135362196</v>
+        <v>135358858</v>
       </c>
       <c r="B259" t="n">
         <v>79373</v>
@@ -29432,10 +29452,10 @@
         <v>658204</v>
       </c>
       <c r="R259" t="n">
-        <v>7328276</v>
+        <v>7328271</v>
       </c>
       <c r="S259" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29464,7 +29484,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -29474,7 +29494,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29489,12 +29509,12 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -29505,32 +29525,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135358857</v>
+        <v>135362196</v>
       </c>
       <c r="B260" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -29540,10 +29560,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>658192</v>
+        <v>658204</v>
       </c>
       <c r="R260" t="n">
-        <v>7328281</v>
+        <v>7328276</v>
       </c>
       <c r="S260" t="n">
         <v>5</v>
@@ -29575,7 +29595,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29585,12 +29605,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29605,15 +29620,131 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B261" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R261" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S261" t="n">
+        <v>5</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX260" t="inlineStr">
+      <c r="AX261" t="inlineStr">
         <is>
           <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
-      <c r="AY260" t="inlineStr">
+      <c r="AY261" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY261"/>
+  <dimension ref="A1:AY262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22965,10 +22965,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135358896</v>
+        <v>135521443</v>
       </c>
       <c r="B202" t="n">
-        <v>80493</v>
+        <v>80492</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22976,21 +22976,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23000,13 +23000,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>658008</v>
+        <v>657679</v>
       </c>
       <c r="R202" t="n">
-        <v>7328268</v>
+        <v>7328375</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23045,7 +23045,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23060,23 +23060,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY202" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135358898</v>
+        <v>135358896</v>
       </c>
       <c r="B203" t="n">
         <v>80493</v>
@@ -23111,10 +23107,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>658006</v>
+        <v>658008</v>
       </c>
       <c r="R203" t="n">
-        <v>7328269</v>
+        <v>7328268</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23146,7 +23142,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23156,7 +23152,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23187,7 +23183,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135363843</v>
+        <v>135358898</v>
       </c>
       <c r="B204" t="n">
         <v>80493</v>
@@ -23222,13 +23218,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>658021</v>
+        <v>658006</v>
       </c>
       <c r="R204" t="n">
-        <v>7328275</v>
+        <v>7328269</v>
       </c>
       <c r="S204" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23257,7 +23253,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23267,7 +23263,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23278,31 +23274,16 @@
       </c>
       <c r="AG204" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -23313,7 +23294,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135363845</v>
+        <v>135363843</v>
       </c>
       <c r="B205" t="n">
         <v>80493</v>
@@ -23348,13 +23329,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>658009</v>
+        <v>658021</v>
       </c>
       <c r="R205" t="n">
-        <v>7328284</v>
+        <v>7328275</v>
       </c>
       <c r="S205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23383,7 +23364,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23393,7 +23374,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23439,7 +23420,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135369268</v>
+        <v>135363845</v>
       </c>
       <c r="B206" t="n">
         <v>80493</v>
@@ -23474,13 +23455,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>657938</v>
+        <v>658009</v>
       </c>
       <c r="R206" t="n">
-        <v>7328289</v>
+        <v>7328284</v>
       </c>
       <c r="S206" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23509,7 +23490,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23519,12 +23500,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23535,23 +23511,42 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY206" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135369280</v>
+        <v>135369268</v>
       </c>
       <c r="B207" t="n">
         <v>80493</v>
@@ -23586,13 +23581,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>657682</v>
+        <v>657938</v>
       </c>
       <c r="R207" t="n">
-        <v>7328376</v>
+        <v>7328289</v>
       </c>
       <c r="S207" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23621,7 +23616,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23631,7 +23626,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -23663,10 +23658,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>135358520</v>
+        <v>135369280</v>
       </c>
       <c r="B208" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23674,21 +23669,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23698,10 +23693,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>658099</v>
+        <v>657682</v>
       </c>
       <c r="R208" t="n">
-        <v>7328289</v>
+        <v>7328376</v>
       </c>
       <c r="S208" t="n">
         <v>8</v>
@@ -23733,7 +23728,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23743,7 +23738,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23758,23 +23758,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135358894</v>
+        <v>135358520</v>
       </c>
       <c r="B209" t="n">
         <v>80499</v>
@@ -23809,13 +23805,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>658009</v>
+        <v>658099</v>
       </c>
       <c r="R209" t="n">
-        <v>7328269</v>
+        <v>7328289</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23844,7 +23840,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23854,7 +23850,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23869,12 +23865,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -23885,7 +23881,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135369269</v>
+        <v>135358894</v>
       </c>
       <c r="B210" t="n">
         <v>80499</v>
@@ -23920,10 +23916,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>657938</v>
+        <v>658009</v>
       </c>
       <c r="R210" t="n">
-        <v>7328289</v>
+        <v>7328269</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -23955,7 +23951,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23965,12 +23961,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23985,22 +23976,26 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135358516</v>
+        <v>135369269</v>
       </c>
       <c r="B211" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24008,21 +24003,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24032,10 +24027,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>658109</v>
+        <v>657938</v>
       </c>
       <c r="R211" t="n">
-        <v>7328286</v>
+        <v>7328289</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24067,7 +24062,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24077,12 +24072,12 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>på låga</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24097,23 +24092,19 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY211" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135358868</v>
+        <v>135358516</v>
       </c>
       <c r="B212" t="n">
         <v>80500</v>
@@ -24148,7 +24139,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>658107</v>
+        <v>658109</v>
       </c>
       <c r="R212" t="n">
         <v>7328286</v>
@@ -24183,7 +24174,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24193,7 +24184,12 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>på låga</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24208,12 +24204,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -24224,7 +24220,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135358892</v>
+        <v>135358868</v>
       </c>
       <c r="B213" t="n">
         <v>80500</v>
@@ -24259,13 +24255,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>658011</v>
+        <v>658107</v>
       </c>
       <c r="R213" t="n">
-        <v>7328274</v>
+        <v>7328286</v>
       </c>
       <c r="S213" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24294,7 +24290,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24304,7 +24300,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24335,7 +24331,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135362212</v>
+        <v>135358892</v>
       </c>
       <c r="B214" t="n">
         <v>80500</v>
@@ -24370,13 +24366,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>658112</v>
+        <v>658011</v>
       </c>
       <c r="R214" t="n">
-        <v>7328279</v>
+        <v>7328274</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24405,7 +24401,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24415,7 +24411,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24430,12 +24426,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -24446,7 +24442,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135363844</v>
+        <v>135362212</v>
       </c>
       <c r="B215" t="n">
         <v>80500</v>
@@ -24481,13 +24477,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>658021</v>
+        <v>658112</v>
       </c>
       <c r="R215" t="n">
-        <v>7328275</v>
+        <v>7328279</v>
       </c>
       <c r="S215" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24516,7 +24512,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24526,7 +24522,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24537,31 +24533,16 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -24572,53 +24553,48 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135357841</v>
+        <v>135363844</v>
       </c>
       <c r="B216" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>658035</v>
+        <v>658021</v>
       </c>
       <c r="R216" t="n">
-        <v>7328397</v>
+        <v>7328275</v>
       </c>
       <c r="S216" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24647,7 +24623,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -24657,12 +24633,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24673,23 +24644,42 @@
       </c>
       <c r="AG216" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY216" t="inlineStr"/>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135357843</v>
+        <v>135357841</v>
       </c>
       <c r="B217" t="n">
         <v>57975</v>
@@ -24720,7 +24710,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24729,10 +24719,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>658016</v>
+        <v>658035</v>
       </c>
       <c r="R217" t="n">
-        <v>7328389</v>
+        <v>7328397</v>
       </c>
       <c r="S217" t="n">
         <v>3</v>
@@ -24764,7 +24754,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24774,12 +24764,12 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24806,7 +24796,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135357845</v>
+        <v>135357843</v>
       </c>
       <c r="B218" t="n">
         <v>57975</v>
@@ -24837,7 +24827,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -24846,10 +24836,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>657975</v>
+        <v>658016</v>
       </c>
       <c r="R218" t="n">
-        <v>7328406</v>
+        <v>7328389</v>
       </c>
       <c r="S218" t="n">
         <v>3</v>
@@ -24881,7 +24871,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24891,12 +24881,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24923,7 +24913,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135358865</v>
+        <v>135357845</v>
       </c>
       <c r="B219" t="n">
         <v>57975</v>
@@ -24952,19 +24942,24 @@
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>658125</v>
+        <v>657975</v>
       </c>
       <c r="R219" t="n">
-        <v>7328274</v>
+        <v>7328406</v>
       </c>
       <c r="S219" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24993,7 +24988,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25003,12 +24998,12 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25023,48 +25018,44 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY219" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135369279</v>
+        <v>135358865</v>
       </c>
       <c r="B220" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25074,13 +25065,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>657744</v>
+        <v>658125</v>
       </c>
       <c r="R220" t="n">
-        <v>7328367</v>
+        <v>7328274</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -25109,7 +25100,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25119,12 +25110,12 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Fågelfjädrar efter tjäder.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25139,22 +25130,26 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY220" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135358873</v>
+        <v>135369279</v>
       </c>
       <c r="B221" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25162,21 +25157,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25186,13 +25181,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>658080</v>
+        <v>657744</v>
       </c>
       <c r="R221" t="n">
-        <v>7328262</v>
+        <v>7328367</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25221,7 +25216,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25231,7 +25226,12 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Fågelfjädrar efter tjäder.</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25246,48 +25246,44 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135357847</v>
+        <v>135358873</v>
       </c>
       <c r="B222" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25297,13 +25293,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>657855</v>
+        <v>658080</v>
       </c>
       <c r="R222" t="n">
-        <v>7328383</v>
+        <v>7328262</v>
       </c>
       <c r="S222" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25332,7 +25328,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25342,7 +25338,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25357,19 +25353,23 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135358530</v>
+        <v>135357847</v>
       </c>
       <c r="B223" t="n">
         <v>58136</v>
@@ -25404,13 +25404,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>657916</v>
+        <v>657855</v>
       </c>
       <c r="R223" t="n">
-        <v>7328337</v>
+        <v>7328383</v>
       </c>
       <c r="S223" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25464,23 +25464,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY223" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135358916</v>
+        <v>135358530</v>
       </c>
       <c r="B224" t="n">
         <v>58136</v>
@@ -25515,13 +25511,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>657914</v>
+        <v>657916</v>
       </c>
       <c r="R224" t="n">
-        <v>7328307</v>
+        <v>7328337</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25550,7 +25546,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25560,7 +25556,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25575,12 +25571,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25591,7 +25587,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135358921</v>
+        <v>135358916</v>
       </c>
       <c r="B225" t="n">
         <v>58136</v>
@@ -25626,10 +25622,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>657875</v>
+        <v>657914</v>
       </c>
       <c r="R225" t="n">
-        <v>7328357</v>
+        <v>7328307</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -25661,7 +25657,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25671,7 +25667,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25702,7 +25698,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135435470</v>
+        <v>135358921</v>
       </c>
       <c r="B226" t="n">
         <v>58136</v>
@@ -25730,24 +25726,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>657931</v>
+        <v>657875</v>
       </c>
       <c r="R226" t="n">
-        <v>7328314</v>
+        <v>7328357</v>
       </c>
       <c r="S226" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25776,7 +25768,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25786,7 +25778,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25801,12 +25793,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -25817,10 +25809,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135358529</v>
+        <v>135435470</v>
       </c>
       <c r="B227" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25828,37 +25820,41 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>657920</v>
+        <v>657931</v>
       </c>
       <c r="R227" t="n">
-        <v>7328326</v>
+        <v>7328314</v>
       </c>
       <c r="S227" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25887,7 +25883,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25897,12 +25893,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>3st</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25917,12 +25908,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -25933,7 +25924,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135362228</v>
+        <v>135358529</v>
       </c>
       <c r="B228" t="n">
         <v>58079</v>
@@ -25962,23 +25953,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>657944</v>
+        <v>657920</v>
       </c>
       <c r="R228" t="n">
-        <v>7328343</v>
+        <v>7328326</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26007,7 +25994,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26017,7 +26004,12 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26032,12 +26024,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26048,27 +26040,27 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135358864</v>
+        <v>135362228</v>
       </c>
       <c r="B229" t="n">
-        <v>5201</v>
+        <v>58079</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -26077,19 +26069,23 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>658134</v>
+        <v>657944</v>
       </c>
       <c r="R229" t="n">
-        <v>7328300</v>
+        <v>7328343</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26118,7 +26114,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26128,7 +26124,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26143,12 +26139,12 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -26159,53 +26155,48 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135435699</v>
+        <v>135358864</v>
       </c>
       <c r="B230" t="n">
-        <v>41606</v>
+        <v>5201</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>215713</v>
+        <v>105930</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>657973</v>
+        <v>658134</v>
       </c>
       <c r="R230" t="n">
-        <v>7328356</v>
+        <v>7328300</v>
       </c>
       <c r="S230" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26229,27 +26220,22 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>01:45</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>LepiLED Maxi med UV och synligt ljus i VUKU-garderob</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26264,12 +26250,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jorma Salmgren, Laura Dobrandt</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -26280,60 +26266,53 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135357260</v>
+        <v>135435699</v>
       </c>
       <c r="B231" t="n">
-        <v>99195</v>
+        <v>41606</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>657949</v>
+        <v>657973</v>
       </c>
       <c r="R231" t="n">
-        <v>7328433</v>
+        <v>7328356</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26357,27 +26336,27 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>8 stänglar</t>
+          <t>LepiLED Maxi med UV och synligt ljus i VUKU-garderob</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26386,19 +26365,18 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson, Jorma Salmgren, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -26409,48 +26387,60 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135357535</v>
+        <v>135357260</v>
       </c>
       <c r="B232" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>658001</v>
+        <v>657949</v>
       </c>
       <c r="R232" t="n">
-        <v>7328390</v>
+        <v>7328433</v>
       </c>
       <c r="S232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26479,7 +26469,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26489,7 +26479,12 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26498,18 +26493,19 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -26520,7 +26516,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135358537</v>
+        <v>135357535</v>
       </c>
       <c r="B233" t="n">
         <v>106309</v>
@@ -26551,17 +26547,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>657761</v>
+        <v>658001</v>
       </c>
       <c r="R233" t="n">
-        <v>7328385</v>
+        <v>7328390</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26590,7 +26586,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26600,7 +26596,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26615,12 +26611,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -26631,10 +26627,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135358540</v>
+        <v>135358537</v>
       </c>
       <c r="B234" t="n">
-        <v>98066</v>
+        <v>106309</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26642,21 +26638,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26666,13 +26662,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>657728</v>
+        <v>657761</v>
       </c>
       <c r="R234" t="n">
-        <v>7328365</v>
+        <v>7328385</v>
       </c>
       <c r="S234" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26701,7 +26697,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26711,7 +26707,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26742,10 +26738,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135357257</v>
+        <v>135358540</v>
       </c>
       <c r="B235" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26753,21 +26749,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26777,13 +26773,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>657988</v>
+        <v>657728</v>
       </c>
       <c r="R235" t="n">
-        <v>7328384</v>
+        <v>7328365</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26812,7 +26808,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26822,7 +26818,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26837,12 +26833,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -26853,7 +26849,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135357530</v>
+        <v>135357257</v>
       </c>
       <c r="B236" t="n">
         <v>99217</v>
@@ -26884,14 +26880,14 @@
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>657995</v>
+        <v>657988</v>
       </c>
       <c r="R236" t="n">
-        <v>7328356</v>
+        <v>7328384</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -26923,7 +26919,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26933,12 +26929,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Elin G</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26953,12 +26944,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26969,7 +26960,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135358927</v>
+        <v>135357530</v>
       </c>
       <c r="B237" t="n">
         <v>99217</v>
@@ -27000,14 +26991,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>657781</v>
+        <v>657995</v>
       </c>
       <c r="R237" t="n">
-        <v>7328332</v>
+        <v>7328356</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -27039,7 +27030,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27049,7 +27040,12 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Elin G</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27064,12 +27060,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27080,7 +27076,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135362223</v>
+        <v>135358927</v>
       </c>
       <c r="B238" t="n">
         <v>99217</v>
@@ -27115,10 +27111,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>658012</v>
+        <v>657781</v>
       </c>
       <c r="R238" t="n">
-        <v>7328314</v>
+        <v>7328332</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -27150,7 +27146,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27160,7 +27156,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27175,12 +27171,12 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27191,7 +27187,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135363849</v>
+        <v>135362223</v>
       </c>
       <c r="B239" t="n">
         <v>99217</v>
@@ -27226,10 +27222,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>657813</v>
+        <v>658012</v>
       </c>
       <c r="R239" t="n">
-        <v>7328352</v>
+        <v>7328314</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -27261,7 +27257,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27271,7 +27267,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27286,12 +27282,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -27302,7 +27298,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135363851</v>
+        <v>135363849</v>
       </c>
       <c r="B240" t="n">
         <v>99217</v>
@@ -27337,10 +27333,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>657575</v>
+        <v>657813</v>
       </c>
       <c r="R240" t="n">
-        <v>7328321</v>
+        <v>7328352</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -27372,7 +27368,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27382,7 +27378,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27413,10 +27409,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135357533</v>
+        <v>135363851</v>
       </c>
       <c r="B241" t="n">
-        <v>100806</v>
+        <v>99217</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27424,34 +27420,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>222584</v>
+        <v>221952</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>657997</v>
+        <v>657575</v>
       </c>
       <c r="R241" t="n">
-        <v>7328373</v>
+        <v>7328321</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -27483,7 +27479,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27493,7 +27489,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27508,12 +27504,12 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -27524,7 +27520,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135358926</v>
+        <v>135357533</v>
       </c>
       <c r="B242" t="n">
         <v>100806</v>
@@ -27555,17 +27551,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>657781</v>
+        <v>657997</v>
       </c>
       <c r="R242" t="n">
-        <v>7328326</v>
+        <v>7328373</v>
       </c>
       <c r="S242" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27594,7 +27590,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27604,7 +27600,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27619,12 +27615,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27635,32 +27631,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135358920</v>
+        <v>135358926</v>
       </c>
       <c r="B243" t="n">
-        <v>79963</v>
+        <v>100806</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>229821</v>
+        <v>222584</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27670,13 +27666,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>657852</v>
+        <v>657781</v>
       </c>
       <c r="R243" t="n">
-        <v>7328299</v>
+        <v>7328326</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27705,7 +27701,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27715,7 +27711,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27746,7 +27742,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135521161</v>
+        <v>135358920</v>
       </c>
       <c r="B244" t="n">
         <v>79963</v>
@@ -27775,22 +27771,19 @@
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>657847</v>
+        <v>657852</v>
       </c>
       <c r="R244" t="n">
-        <v>7328292</v>
+        <v>7328299</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27819,7 +27812,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27829,7 +27822,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27838,87 +27831,73 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY244" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135358863</v>
+        <v>135521161</v>
       </c>
       <c r="B245" t="n">
-        <v>95840</v>
+        <v>79963</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1004672</v>
+        <v>229821</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>658147</v>
+        <v>657847</v>
       </c>
       <c r="R245" t="n">
-        <v>7328286</v>
+        <v>7328292</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27947,7 +27926,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27957,7 +27936,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27966,54 +27945,71 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY245" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135357825</v>
+        <v>135358863</v>
       </c>
       <c r="B246" t="n">
-        <v>92245</v>
+        <v>95840</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>658</v>
+        <v>1004672</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28023,13 +28019,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>658190</v>
+        <v>658147</v>
       </c>
       <c r="R246" t="n">
-        <v>7328207</v>
+        <v>7328286</v>
       </c>
       <c r="S246" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28058,7 +28054,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28068,7 +28064,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28083,22 +28079,26 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY246" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135362199</v>
+        <v>135357825</v>
       </c>
       <c r="B247" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28106,21 +28106,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>658211</v>
+        <v>658190</v>
       </c>
       <c r="R247" t="n">
-        <v>7328232</v>
+        <v>7328207</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28190,26 +28190,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY247" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135357823</v>
+        <v>135362199</v>
       </c>
       <c r="B248" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28217,21 +28213,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28241,13 +28237,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>658198</v>
+        <v>658211</v>
       </c>
       <c r="R248" t="n">
-        <v>7328244</v>
+        <v>7328232</v>
       </c>
       <c r="S248" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28276,7 +28272,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28286,7 +28282,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28301,22 +28297,26 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY248" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135362200</v>
+        <v>135357823</v>
       </c>
       <c r="B249" t="n">
-        <v>83222</v>
+        <v>91970</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28324,21 +28324,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28348,13 +28348,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>658209</v>
+        <v>658198</v>
       </c>
       <c r="R249" t="n">
-        <v>7328233</v>
+        <v>7328244</v>
       </c>
       <c r="S249" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28393,12 +28393,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28413,48 +28408,44 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY249" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135358229</v>
+        <v>135362200</v>
       </c>
       <c r="B250" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28464,10 +28455,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>658194</v>
+        <v>658209</v>
       </c>
       <c r="R250" t="n">
-        <v>7328255</v>
+        <v>7328233</v>
       </c>
       <c r="S250" t="n">
         <v>5</v>
@@ -28497,9 +28488,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28514,12 +28520,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -28530,7 +28536,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135358506</v>
+        <v>135358229</v>
       </c>
       <c r="B251" t="n">
         <v>79373</v>
@@ -28565,13 +28571,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>658212</v>
+        <v>658194</v>
       </c>
       <c r="R251" t="n">
-        <v>7328246</v>
+        <v>7328255</v>
       </c>
       <c r="S251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28598,19 +28604,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28625,12 +28621,12 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -28641,7 +28637,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135358507</v>
+        <v>135358506</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28676,13 +28672,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>658198</v>
+        <v>658212</v>
       </c>
       <c r="R252" t="n">
-        <v>7328199</v>
+        <v>7328246</v>
       </c>
       <c r="S252" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28711,7 +28707,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28721,7 +28717,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28752,7 +28748,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135358508</v>
+        <v>135358507</v>
       </c>
       <c r="B253" t="n">
         <v>79373</v>
@@ -28787,13 +28783,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>658194</v>
+        <v>658198</v>
       </c>
       <c r="R253" t="n">
-        <v>7328167</v>
+        <v>7328199</v>
       </c>
       <c r="S253" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28822,7 +28818,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28832,7 +28828,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28863,7 +28859,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135362197</v>
+        <v>135358508</v>
       </c>
       <c r="B254" t="n">
         <v>79373</v>
@@ -28898,13 +28894,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>658207</v>
+        <v>658194</v>
       </c>
       <c r="R254" t="n">
-        <v>7328242</v>
+        <v>7328167</v>
       </c>
       <c r="S254" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28933,7 +28929,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28943,7 +28939,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28958,12 +28954,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -28974,7 +28970,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135362198</v>
+        <v>135362197</v>
       </c>
       <c r="B255" t="n">
         <v>79373</v>
@@ -29009,10 +29005,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>658209</v>
+        <v>658207</v>
       </c>
       <c r="R255" t="n">
-        <v>7328235</v>
+        <v>7328242</v>
       </c>
       <c r="S255" t="n">
         <v>5</v>
@@ -29044,7 +29040,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29054,7 +29050,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29085,53 +29081,48 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135357824</v>
+        <v>135362198</v>
       </c>
       <c r="B256" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>658192</v>
+        <v>658209</v>
       </c>
       <c r="R256" t="n">
-        <v>7328225</v>
+        <v>7328235</v>
       </c>
       <c r="S256" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29160,7 +29151,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -29170,12 +29161,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29190,60 +29176,69 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY256" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135358230</v>
+        <v>135357824</v>
       </c>
       <c r="B257" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>658217</v>
+        <v>658192</v>
       </c>
       <c r="R257" t="n">
-        <v>7328285</v>
+        <v>7328225</v>
       </c>
       <c r="S257" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29270,9 +29265,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29287,23 +29297,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY257" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135358505</v>
+        <v>135358230</v>
       </c>
       <c r="B258" t="n">
         <v>79373</v>
@@ -29338,13 +29344,13 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>658205</v>
+        <v>658217</v>
       </c>
       <c r="R258" t="n">
-        <v>7328283</v>
+        <v>7328285</v>
       </c>
       <c r="S258" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29371,19 +29377,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29398,12 +29394,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -29414,7 +29410,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135358858</v>
+        <v>135358505</v>
       </c>
       <c r="B259" t="n">
         <v>79373</v>
@@ -29449,13 +29445,13 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>658204</v>
+        <v>658205</v>
       </c>
       <c r="R259" t="n">
-        <v>7328271</v>
+        <v>7328283</v>
       </c>
       <c r="S259" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29484,7 +29480,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -29494,7 +29490,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29509,12 +29505,12 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -29525,7 +29521,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135362196</v>
+        <v>135358858</v>
       </c>
       <c r="B260" t="n">
         <v>79373</v>
@@ -29563,10 +29559,10 @@
         <v>658204</v>
       </c>
       <c r="R260" t="n">
-        <v>7328276</v>
+        <v>7328271</v>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29595,7 +29591,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29605,7 +29601,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29620,12 +29616,12 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -29636,32 +29632,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>135358857</v>
+        <v>135362196</v>
       </c>
       <c r="B261" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29671,10 +29667,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>658192</v>
+        <v>658204</v>
       </c>
       <c r="R261" t="n">
-        <v>7328281</v>
+        <v>7328276</v>
       </c>
       <c r="S261" t="n">
         <v>5</v>
@@ -29706,7 +29702,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -29716,12 +29712,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Äldre hackspår</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29736,15 +29727,131 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>135358857</v>
+      </c>
+      <c r="B262" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>658192</v>
+      </c>
+      <c r="R262" t="n">
+        <v>7328281</v>
+      </c>
+      <c r="S262" t="n">
+        <v>5</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX261" t="inlineStr">
+      <c r="AX262" t="inlineStr">
         <is>
           <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
-      <c r="AY261" t="inlineStr">
+      <c r="AY262" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -928,6 +928,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
@@ -988,6 +991,7 @@
       <c r="AE4" t="b">
         <v>1</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,7 +1006,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -22994,6 +23002,9 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
@@ -23054,6 +23065,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -23068,7 +23080,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY202" t="inlineStr"/>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -27959,14 +27975,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -27980,7 +27991,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY245" t="inlineStr"/>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY262"/>
+  <dimension ref="A1:AZ262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357830</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135520047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369274</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363841</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358874</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369261</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369262</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362204</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,6 +2312,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357827</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357831</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2460,6 +2540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357241</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358900</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369260</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2795,6 +2890,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369263</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2907,6 +3007,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369264</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3015,6 +3120,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357826</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357246</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3246,6 +3361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358513</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3358,6 +3478,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369275</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356932</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3580,6 +3710,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356933</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3691,6 +3826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357242</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3802,6 +3942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357243</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3913,6 +4058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357245</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4024,6 +4174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357521</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4135,6 +4290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357522</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4236,6 +4396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358232</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4337,6 +4502,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358233</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4438,6 +4608,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358234</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4549,6 +4724,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358509</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4660,6 +4840,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358510</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4771,6 +4956,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358877</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4882,6 +5072,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362201</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4993,6 +5188,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362205</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5104,6 +5304,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362206</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5215,6 +5420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362207</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5326,6 +5536,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362209</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5437,6 +5652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362210</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5548,6 +5768,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363842</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5660,6 +5885,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369259</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5772,6 +6002,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369273</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5883,6 +6118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357524</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5994,6 +6234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356934</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6105,6 +6350,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357244</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6217,6 +6467,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369265</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6328,6 +6583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358512</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6439,6 +6699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358890</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6565,6 +6830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363839</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6677,6 +6947,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369271</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6788,6 +7063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357249</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6899,6 +7179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357247</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7010,6 +7295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358889</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7126,6 +7416,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362208</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7252,6 +7547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363838</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7364,6 +7664,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369270</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7481,6 +7786,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357829</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7597,6 +7907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363836</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7708,6 +8023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358514</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7819,6 +8139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363837</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7930,6 +8255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363840</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8041,6 +8371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362203</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8152,6 +8487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358925</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8278,6 +8618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363850</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8389,6 +8734,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357256</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8505,6 +8855,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357527</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8621,6 +8976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357531</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8732,6 +9092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357538</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8858,6 +9223,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363848</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8969,6 +9339,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356943</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9080,6 +9455,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356953</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9191,6 +9571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357254</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9302,6 +9687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357258</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9413,6 +9803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357261</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9524,6 +9919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357540</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9640,6 +10040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357543</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9747,6 +10152,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357837</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9854,6 +10264,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357842</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9965,6 +10380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358539</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10076,6 +10496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358870</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10187,6 +10612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358879</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10298,6 +10728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358923</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10414,6 +10849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362243</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10523,6 +10963,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356944</t>
         </is>
       </c>
     </row>
@@ -10645,6 +11090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357526</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10756,6 +11206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357529</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10867,6 +11322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358523</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10978,6 +11438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358526</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11089,6 +11554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358531</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11200,6 +11670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358534</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11311,6 +11786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358859</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11422,6 +11902,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358869</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11533,6 +12018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358887</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11644,6 +12134,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358906</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11755,6 +12250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358908</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11866,6 +12366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358915</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11977,6 +12482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358917</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12088,6 +12598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362242</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12200,6 +12715,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369267</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12308,6 +12828,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357838</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12405,6 +12930,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135312324</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12512,6 +13042,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357835</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12628,6 +13163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362216</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12739,6 +13279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357255</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12850,6 +13395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358867</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12961,6 +13511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358919</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13072,6 +13627,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358922</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13183,6 +13743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356949</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13290,6 +13855,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357844</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13397,6 +13967,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357846</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13523,6 +14098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363847</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13634,6 +14214,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357252</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13745,6 +14330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358860</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13861,6 +14451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358872</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13972,6 +14567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358902</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14083,6 +14683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358911</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14194,6 +14799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358913</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14305,6 +14915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357536</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14416,6 +15031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357539</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14527,6 +15147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435690</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14638,6 +15263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435692</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14749,6 +15379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356945</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14860,6 +15495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356947</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14971,6 +15611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356936</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15082,6 +15727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356938</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15193,6 +15843,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356939</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15304,6 +15959,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356940</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15415,6 +16075,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356941</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15526,6 +16191,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356946</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15637,6 +16307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356948</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15748,6 +16423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356951</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15859,6 +16539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356952</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15970,6 +16655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357250</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16081,6 +16771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357251</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16192,6 +16887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357253</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16303,6 +17003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357259</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16414,6 +17119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357262</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16525,6 +17235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357528</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16636,6 +17351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357537</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16747,6 +17467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357546</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16858,6 +17583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357547</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16965,6 +17695,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357833</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17077,6 +17812,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357834</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17184,6 +17924,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357836</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17296,6 +18041,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357839</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17407,6 +18157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358515</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17518,6 +18273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358519</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17634,6 +18394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358521</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17745,6 +18510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358525</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17856,6 +18626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358532</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17967,6 +18742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358533</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18078,6 +18858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358536</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18189,6 +18974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358538</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18300,6 +19090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358861</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18411,6 +19206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358866</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18522,6 +19322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358871</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18633,6 +19438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358904</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18744,6 +19554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358909</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18855,6 +19670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358912</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18966,6 +19786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358914</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19077,6 +19902,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358918</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19188,6 +20018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358924</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19299,6 +20134,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362213</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19410,6 +20250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362215</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19521,6 +20366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362218</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19632,6 +20482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362219</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19743,6 +20598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362220</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19854,6 +20714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362221</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19965,6 +20830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362224</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20076,6 +20946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362225</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20187,6 +21062,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362226</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20298,6 +21178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362227</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20409,6 +21294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362230</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20520,6 +21410,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362231</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20631,6 +21526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362232</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20742,6 +21642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362233</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20853,6 +21758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362235</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20964,6 +21874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362236</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21075,6 +21990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362237</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21186,6 +22106,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362238</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21297,6 +22222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362239</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21408,6 +22338,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362240</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21519,6 +22454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362241</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21630,6 +22570,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362244</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21741,6 +22686,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362245</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21852,6 +22802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362246</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21963,6 +22918,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362247</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22074,6 +23034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363846</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22186,6 +23151,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369266</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22298,6 +23268,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369277</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22410,6 +23385,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369278</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22521,6 +23501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358910</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22632,6 +23617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356935</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22743,6 +23733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356950</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22859,6 +23854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357523</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22968,6 +23968,11 @@
       <c r="AY201" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358862</t>
         </is>
       </c>
     </row>
@@ -23085,6 +24090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521443</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23196,6 +24206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358896</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23307,6 +24322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358898</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23433,6 +24453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363843</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23559,6 +24584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363845</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23671,6 +24701,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369268</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23783,6 +24818,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369280</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23894,6 +24934,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358520</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24005,6 +25050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358894</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24117,6 +25167,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369269</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24233,6 +25288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358516</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24344,6 +25404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358868</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24455,6 +25520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358892</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24566,6 +25636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362212</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24692,6 +25767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363844</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24809,6 +25889,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357841</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24926,6 +26011,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357843</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25043,6 +26133,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357845</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25159,6 +26254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358865</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25271,6 +26371,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369279</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25382,6 +26487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358873</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25489,6 +26599,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357847</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25600,6 +26715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358530</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25711,6 +26831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358916</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25822,6 +26947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358921</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25937,6 +27067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435470</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26051,6 +27186,11 @@
       <c r="AY228" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358529</t>
         </is>
       </c>
     </row>
@@ -26168,6 +27308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362228</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26279,6 +27424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358864</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26400,6 +27550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435699</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26529,6 +27684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357260</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26640,6 +27800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357535</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26751,6 +27916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358537</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26862,6 +28032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358540</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26973,6 +28148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357257</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27089,6 +28269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357530</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27200,6 +28385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358927</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27311,6 +28501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362223</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27422,6 +28617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363849</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27533,6 +28733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363851</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27644,6 +28849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357533</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27755,6 +28965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358926</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27864,6 +29079,11 @@
       <c r="AY244" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358920</t>
         </is>
       </c>
     </row>
@@ -27996,6 +29216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521161</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28107,6 +29332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358863</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28214,6 +29444,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357825</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28325,6 +29560,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362199</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28432,6 +29672,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357823</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28548,6 +29793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362200</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28649,6 +29899,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358229</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28760,6 +30015,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358506</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28871,6 +30131,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358507</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28982,6 +30247,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358508</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29093,6 +30363,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362197</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29204,6 +30479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362198</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29321,6 +30601,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357824</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29422,6 +30707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358230</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29533,6 +30823,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358505</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29644,6 +30939,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358858</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29755,6 +31055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362196</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29871,8 +31176,276 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Paulina Delin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135362202</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135357830</v>
       </c>
       <c r="B3" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135520047</v>
       </c>
       <c r="B4" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135358883</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>135358885</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135369274</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>135363841</v>
       </c>
       <c r="B8" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>135358874</v>
       </c>
       <c r="B9" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135369261</v>
       </c>
       <c r="B10" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Paulina Delin, Linda Nordström</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         <v>135369262</v>
       </c>
       <c r="B11" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135358881</v>
       </c>
       <c r="B12" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135357828</v>
       </c>
       <c r="B13" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135362204</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>135357827</v>
       </c>
       <c r="B15" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>135357831</v>
       </c>
       <c r="B16" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>135357241</v>
       </c>
       <c r="B17" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>135358900</v>
       </c>
       <c r="B18" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>135369260</v>
       </c>
       <c r="B19" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>135369263</v>
       </c>
       <c r="B20" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135369264</v>
       </c>
       <c r="B21" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>135357826</v>
       </c>
       <c r="B22" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>135357246</v>
       </c>
       <c r="B23" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>135358513</v>
       </c>
       <c r="B24" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135369275</v>
       </c>
       <c r="B25" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
         <v>135356932</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135356933</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>135357242</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135357243</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>135357245</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>135357521</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135357522</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>135358232</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>135358233</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>135358234</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135358509</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135358510</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135358877</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135362201</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135362205</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135362206</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>135362207</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>135362209</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135362210</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>135363842</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>135369259</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135369273</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135357524</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>135356934</v>
       </c>
       <c r="B49" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135357244</v>
       </c>
       <c r="B50" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>135369265</v>
       </c>
       <c r="B51" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6478,7 +6478,7 @@
         <v>135358512</v>
       </c>
       <c r="B52" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>135358890</v>
       </c>
       <c r="B53" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>135363839</v>
       </c>
       <c r="B54" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>135369271</v>
       </c>
       <c r="B55" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>135357249</v>
       </c>
       <c r="B56" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>135357247</v>
       </c>
       <c r="B57" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>135358889</v>
       </c>
       <c r="B58" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>135362208</v>
       </c>
       <c r="B59" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>135363838</v>
       </c>
       <c r="B60" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135369270</v>
       </c>
       <c r="B61" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>135357829</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>135363836</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>135358514</v>
       </c>
       <c r="B64" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135363837</v>
       </c>
       <c r="B65" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>135363840</v>
       </c>
       <c r="B66" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>135362203</v>
       </c>
       <c r="B67" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>135358925</v>
       </c>
       <c r="B68" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>135363850</v>
       </c>
       <c r="B69" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135357256</v>
       </c>
       <c r="B70" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135357527</v>
       </c>
       <c r="B71" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>135357531</v>
       </c>
       <c r="B72" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>135357538</v>
       </c>
       <c r="B73" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>135363848</v>
       </c>
       <c r="B74" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>135356943</v>
       </c>
       <c r="B75" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>135356953</v>
       </c>
       <c r="B76" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>135357254</v>
       </c>
       <c r="B77" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>135357258</v>
       </c>
       <c r="B78" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>135357261</v>
       </c>
       <c r="B79" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>135357540</v>
       </c>
       <c r="B80" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>135357543</v>
       </c>
       <c r="B81" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>135357837</v>
       </c>
       <c r="B82" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>135357842</v>
       </c>
       <c r="B83" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>135358539</v>
       </c>
       <c r="B84" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>135358870</v>
       </c>
       <c r="B85" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>135358879</v>
       </c>
       <c r="B86" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>135358923</v>
       </c>
       <c r="B87" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>135362243</v>
       </c>
       <c r="B88" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>135356944</v>
       </c>
       <c r="B89" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>135357526</v>
       </c>
       <c r="B90" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>135357529</v>
       </c>
       <c r="B91" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>135358523</v>
       </c>
       <c r="B92" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>135358526</v>
       </c>
       <c r="B93" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>135358531</v>
       </c>
       <c r="B94" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>135358534</v>
       </c>
       <c r="B95" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>135358859</v>
       </c>
       <c r="B96" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>135358869</v>
       </c>
       <c r="B97" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>135358887</v>
       </c>
       <c r="B98" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>135358906</v>
       </c>
       <c r="B99" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>135358908</v>
       </c>
       <c r="B100" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135358915</v>
       </c>
       <c r="B101" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>135358917</v>
       </c>
       <c r="B102" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>135362242</v>
       </c>
       <c r="B103" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>135369267</v>
       </c>
       <c r="B104" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>135357838</v>
       </c>
       <c r="B105" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>135312324</v>
       </c>
       <c r="B106" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>135357835</v>
       </c>
       <c r="B107" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>135362216</v>
       </c>
       <c r="B108" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>135357255</v>
       </c>
       <c r="B109" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>135358867</v>
       </c>
       <c r="B110" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>135358919</v>
       </c>
       <c r="B111" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135358922</v>
       </c>
       <c r="B112" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>135356949</v>
       </c>
       <c r="B113" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>135357844</v>
       </c>
       <c r="B114" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>135357846</v>
       </c>
       <c r="B115" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>135363847</v>
       </c>
       <c r="B116" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>135357252</v>
       </c>
       <c r="B117" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>135358860</v>
       </c>
       <c r="B118" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135358872</v>
       </c>
       <c r="B119" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135358902</v>
       </c>
       <c r="B120" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135358911</v>
       </c>
       <c r="B121" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>135358913</v>
       </c>
       <c r="B122" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>135357536</v>
       </c>
       <c r="B123" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>135357539</v>
       </c>
       <c r="B124" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>135435690</v>
       </c>
       <c r="B125" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>135435692</v>
       </c>
       <c r="B126" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>135356945</v>
       </c>
       <c r="B127" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>135356947</v>
       </c>
       <c r="B128" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>135356936</v>
       </c>
       <c r="B129" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>135356938</v>
       </c>
       <c r="B130" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>135356939</v>
       </c>
       <c r="B131" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>135356940</v>
       </c>
       <c r="B132" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>135356941</v>
       </c>
       <c r="B133" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>135356946</v>
       </c>
       <c r="B134" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>135356948</v>
       </c>
       <c r="B135" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>135356951</v>
       </c>
       <c r="B136" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>135356952</v>
       </c>
       <c r="B137" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>135357250</v>
       </c>
       <c r="B138" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>135357251</v>
       </c>
       <c r="B139" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>135357253</v>
       </c>
       <c r="B140" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>135357259</v>
       </c>
       <c r="B141" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>135357262</v>
       </c>
       <c r="B142" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135357528</v>
       </c>
       <c r="B143" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>135357537</v>
       </c>
       <c r="B144" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>135357546</v>
       </c>
       <c r="B145" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>135357547</v>
       </c>
       <c r="B146" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>135357833</v>
       </c>
       <c r="B147" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>135357834</v>
       </c>
       <c r="B148" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>135357836</v>
       </c>
       <c r="B149" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>135357839</v>
       </c>
       <c r="B150" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>135358515</v>
       </c>
       <c r="B151" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>135358519</v>
       </c>
       <c r="B152" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>135358521</v>
       </c>
       <c r="B153" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>135358525</v>
       </c>
       <c r="B154" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>135358532</v>
       </c>
       <c r="B155" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>135358533</v>
       </c>
       <c r="B156" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>135358536</v>
       </c>
       <c r="B157" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>135358538</v>
       </c>
       <c r="B158" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>135358861</v>
       </c>
       <c r="B159" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>135358866</v>
       </c>
       <c r="B160" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>135358871</v>
       </c>
       <c r="B161" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>135358904</v>
       </c>
       <c r="B162" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>135358909</v>
       </c>
       <c r="B163" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>135358912</v>
       </c>
       <c r="B164" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>135358914</v>
       </c>
       <c r="B165" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>135358918</v>
       </c>
       <c r="B166" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>135358924</v>
       </c>
       <c r="B167" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>135362213</v>
       </c>
       <c r="B168" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>135362215</v>
       </c>
       <c r="B169" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135362218</v>
       </c>
       <c r="B170" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>135362219</v>
       </c>
       <c r="B171" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>135362220</v>
       </c>
       <c r="B172" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>135362221</v>
       </c>
       <c r="B173" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>135362224</v>
       </c>
       <c r="B174" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>135362225</v>
       </c>
       <c r="B175" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>135362226</v>
       </c>
       <c r="B176" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>135362227</v>
       </c>
       <c r="B177" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>135362230</v>
       </c>
       <c r="B178" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>135362231</v>
       </c>
       <c r="B179" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>135362232</v>
       </c>
       <c r="B180" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>135362233</v>
       </c>
       <c r="B181" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>135362235</v>
       </c>
       <c r="B182" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>135362236</v>
       </c>
       <c r="B183" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>135362237</v>
       </c>
       <c r="B184" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>135362238</v>
       </c>
       <c r="B185" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>135362239</v>
       </c>
       <c r="B186" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>135362240</v>
       </c>
       <c r="B187" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>135362241</v>
       </c>
       <c r="B188" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135362244</v>
       </c>
       <c r="B189" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>135362245</v>
       </c>
       <c r="B190" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>135362246</v>
       </c>
       <c r="B191" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>135362247</v>
       </c>
       <c r="B192" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>135363846</v>
       </c>
       <c r="B193" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>135369266</v>
       </c>
       <c r="B194" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>135369277</v>
       </c>
       <c r="B195" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135369278</v>
       </c>
       <c r="B196" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>135358910</v>
       </c>
       <c r="B197" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>135356935</v>
       </c>
       <c r="B198" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>135356950</v>
       </c>
       <c r="B199" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>135357523</v>
       </c>
       <c r="B200" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135358862</v>
       </c>
       <c r="B201" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>135521443</v>
       </c>
       <c r="B202" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>135358896</v>
       </c>
       <c r="B203" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>135358898</v>
       </c>
       <c r="B204" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>135363843</v>
       </c>
       <c r="B205" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>135363845</v>
       </c>
       <c r="B206" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>135369268</v>
       </c>
       <c r="B207" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -24712,7 +24712,7 @@
         <v>135369280</v>
       </c>
       <c r="B208" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>135358520</v>
       </c>
       <c r="B209" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>135358894</v>
       </c>
       <c r="B210" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>135369269</v>
       </c>
       <c r="B211" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>135358516</v>
       </c>
       <c r="B212" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>135358868</v>
       </c>
       <c r="B213" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>135358892</v>
       </c>
       <c r="B214" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>135362212</v>
       </c>
       <c r="B215" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>135363844</v>
       </c>
       <c r="B216" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>135357841</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>135357843</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>135357845</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>135358865</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>135369279</v>
       </c>
       <c r="B221" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>135357847</v>
       </c>
       <c r="B223" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>135358530</v>
       </c>
       <c r="B224" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>135358916</v>
       </c>
       <c r="B225" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>135358921</v>
       </c>
       <c r="B226" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>135435470</v>
       </c>
       <c r="B227" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>135358529</v>
       </c>
       <c r="B228" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>135362228</v>
       </c>
       <c r="B229" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>135435699</v>
       </c>
       <c r="B231" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>135357260</v>
       </c>
       <c r="B232" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>135357535</v>
       </c>
       <c r="B233" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>135358537</v>
       </c>
       <c r="B234" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>135358540</v>
       </c>
       <c r="B235" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>135357257</v>
       </c>
       <c r="B236" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>135357530</v>
       </c>
       <c r="B237" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>135358927</v>
       </c>
       <c r="B238" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>135362223</v>
       </c>
       <c r="B239" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>135363849</v>
       </c>
       <c r="B240" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>135363851</v>
       </c>
       <c r="B241" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>135357533</v>
       </c>
       <c r="B242" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>135358926</v>
       </c>
       <c r="B243" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>135358920</v>
       </c>
       <c r="B244" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>135521161</v>
       </c>
       <c r="B245" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>135358863</v>
       </c>
       <c r="B246" t="n">
-        <v>95840</v>
+        <v>95884</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>135357825</v>
       </c>
       <c r="B247" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>135362199</v>
       </c>
       <c r="B248" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>135357823</v>
       </c>
       <c r="B249" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>135362200</v>
       </c>
       <c r="B250" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>135358229</v>
       </c>
       <c r="B251" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>135358506</v>
       </c>
       <c r="B252" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>135358507</v>
       </c>
       <c r="B253" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>135358508</v>
       </c>
       <c r="B254" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>135362197</v>
       </c>
       <c r="B255" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>135362198</v>
       </c>
       <c r="B256" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>135357824</v>
       </c>
       <c r="B257" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>135358230</v>
       </c>
       <c r="B258" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>135358505</v>
       </c>
       <c r="B259" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>135358858</v>
       </c>
       <c r="B260" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>135362196</v>
       </c>
       <c r="B261" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>135358857</v>
       </c>
       <c r="B262" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135362202</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135357830</v>
       </c>
       <c r="B3" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135520047</v>
       </c>
       <c r="B4" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135358883</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>135358885</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135369274</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>135363841</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135358881</v>
       </c>
       <c r="B12" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135357828</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135362204</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>135357827</v>
       </c>
       <c r="B15" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>135357831</v>
       </c>
       <c r="B16" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>135357826</v>
       </c>
       <c r="B22" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>135363836</v>
       </c>
       <c r="B63" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>135358514</v>
       </c>
       <c r="B64" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135363837</v>
       </c>
       <c r="B65" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>135363840</v>
       </c>
       <c r="B66" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>135362203</v>
       </c>
       <c r="B67" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>135358925</v>
       </c>
       <c r="B68" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>135363850</v>
       </c>
       <c r="B69" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>135357256</v>
       </c>
       <c r="B70" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>135357527</v>
       </c>
       <c r="B71" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>135357531</v>
       </c>
       <c r="B72" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>135357538</v>
       </c>
       <c r="B73" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>135363848</v>
       </c>
       <c r="B74" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>135356943</v>
       </c>
       <c r="B75" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>135356953</v>
       </c>
       <c r="B76" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>135357254</v>
       </c>
       <c r="B77" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>135357258</v>
       </c>
       <c r="B78" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>135357261</v>
       </c>
       <c r="B79" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>135357540</v>
       </c>
       <c r="B80" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>135357543</v>
       </c>
       <c r="B81" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>135357837</v>
       </c>
       <c r="B82" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>135357842</v>
       </c>
       <c r="B83" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>135358539</v>
       </c>
       <c r="B84" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>135358870</v>
       </c>
       <c r="B85" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>135358879</v>
       </c>
       <c r="B86" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>135358923</v>
       </c>
       <c r="B87" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>135362243</v>
       </c>
       <c r="B88" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>135357838</v>
       </c>
       <c r="B105" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>135312324</v>
       </c>
       <c r="B106" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>135357835</v>
       </c>
       <c r="B107" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>135362216</v>
       </c>
       <c r="B108" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>135357255</v>
       </c>
       <c r="B109" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>135358867</v>
       </c>
       <c r="B110" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>135358919</v>
       </c>
       <c r="B111" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135358922</v>
       </c>
       <c r="B112" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>135356949</v>
       </c>
       <c r="B113" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>135357844</v>
       </c>
       <c r="B114" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>135357846</v>
       </c>
       <c r="B115" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>135363847</v>
       </c>
       <c r="B116" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>135357539</v>
       </c>
       <c r="B124" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>135435690</v>
       </c>
       <c r="B125" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>135435692</v>
       </c>
       <c r="B126" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>135356945</v>
       </c>
       <c r="B127" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>135356947</v>
       </c>
       <c r="B128" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>135357260</v>
       </c>
       <c r="B232" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>135357535</v>
       </c>
       <c r="B233" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>135358537</v>
       </c>
       <c r="B234" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>135358540</v>
       </c>
       <c r="B235" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>135357257</v>
       </c>
       <c r="B236" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>135357530</v>
       </c>
       <c r="B237" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>135358927</v>
       </c>
       <c r="B238" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>135362223</v>
       </c>
       <c r="B239" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>135363849</v>
       </c>
       <c r="B240" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>135363851</v>
       </c>
       <c r="B241" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>135357533</v>
       </c>
       <c r="B242" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>135358926</v>
       </c>
       <c r="B243" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>135358863</v>
       </c>
       <c r="B246" t="n">
-        <v>95916</v>
+        <v>95918</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>135357825</v>
       </c>
       <c r="B247" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>135357823</v>
       </c>
       <c r="B249" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135520047</v>
       </c>
       <c r="B4" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>135363841</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>92637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>135358513</v>
       </c>
       <c r="B24" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>135363842</v>
       </c>
       <c r="B45" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>135358512</v>
       </c>
       <c r="B52" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>135363839</v>
       </c>
       <c r="B54" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>135363838</v>
       </c>
       <c r="B60" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>135363836</v>
       </c>
       <c r="B63" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>135358514</v>
       </c>
       <c r="B64" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135363837</v>
       </c>
       <c r="B65" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>135363840</v>
       </c>
       <c r="B66" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>135363850</v>
       </c>
       <c r="B69" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>135363848</v>
       </c>
       <c r="B74" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>135358539</v>
       </c>
       <c r="B84" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>135358523</v>
       </c>
       <c r="B92" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>135358526</v>
       </c>
       <c r="B93" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>135358534</v>
       </c>
       <c r="B95" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>135363847</v>
       </c>
       <c r="B116" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>135435690</v>
       </c>
       <c r="B125" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>135435692</v>
       </c>
       <c r="B126" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>135363846</v>
       </c>
       <c r="B193" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>135521443</v>
       </c>
       <c r="B202" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>135363843</v>
       </c>
       <c r="B205" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>135363845</v>
       </c>
       <c r="B206" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>135358520</v>
       </c>
       <c r="B209" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>135358516</v>
       </c>
       <c r="B212" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>135363844</v>
       </c>
       <c r="B216" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>135435470</v>
       </c>
       <c r="B227" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>135435699</v>
       </c>
       <c r="B231" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>135358540</v>
       </c>
       <c r="B235" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>135363849</v>
       </c>
       <c r="B240" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>135363851</v>
       </c>
       <c r="B241" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>135521161</v>
       </c>
       <c r="B245" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>135358506</v>
       </c>
       <c r="B252" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135520047</v>
       </c>
       <c r="B4" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>135358513</v>
       </c>
       <c r="B24" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>135358512</v>
       </c>
       <c r="B52" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>135358514</v>
       </c>
       <c r="B64" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>135358539</v>
       </c>
       <c r="B84" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>135358523</v>
       </c>
       <c r="B92" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>135358526</v>
       </c>
       <c r="B93" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>135358534</v>
       </c>
       <c r="B95" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>135521443</v>
       </c>
       <c r="B202" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>135358520</v>
       </c>
       <c r="B209" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>135358516</v>
       </c>
       <c r="B212" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>135358540</v>
       </c>
       <c r="B235" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>135521161</v>
       </c>
       <c r="B245" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>135358506</v>
       </c>
       <c r="B252" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>136336944</v>
       </c>
       <c r="B240" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>136336945</v>
       </c>
       <c r="B241" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>136336935</v>
       </c>
       <c r="B246" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>136336931</v>
       </c>
       <c r="B271" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>136336939</v>
       </c>
       <c r="B272" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>136336948</v>
       </c>
       <c r="B273" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>136336954</v>
       </c>
       <c r="B274" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>136336960</v>
       </c>
       <c r="B275" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>136336965</v>
       </c>
       <c r="B276" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>136336944</v>
       </c>
       <c r="B240" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>136336945</v>
       </c>
       <c r="B241" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>136336935</v>
       </c>
       <c r="B246" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>136336931</v>
       </c>
       <c r="B271" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>136336939</v>
       </c>
       <c r="B272" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>136336948</v>
       </c>
       <c r="B273" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>136336954</v>
       </c>
       <c r="B274" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>136336960</v>
       </c>
       <c r="B275" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>136336965</v>
       </c>
       <c r="B276" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>136336931</v>
       </c>
       <c r="B271" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>136336939</v>
       </c>
       <c r="B272" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>136336948</v>
       </c>
       <c r="B273" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>136336954</v>
       </c>
       <c r="B274" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>136336960</v>
       </c>
       <c r="B275" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>136336965</v>
       </c>
       <c r="B276" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
